--- a/research/traditional_assets/database/data/slovenia/slovenia_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/slovenia/slovenia_shipbuilding_marine.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0967720572940558</v>
+        <v>0.09662464038519709</v>
       </c>
       <c r="C2">
-        <v>684.0511667822698</v>
+        <v>678.4170820435822</v>
       </c>
       <c r="D2">
-        <v>584.9511667822698</v>
+        <v>586.2110820435822</v>
       </c>
       <c r="E2">
-        <v>-109.6</v>
+        <v>-102.706</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.894</v>
       </c>
       <c r="G2">
         <v>99.09999999999999</v>
@@ -1451,28 +1451,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3467682</v>
       </c>
       <c r="N2">
-        <v>66.19999999999999</v>
+        <v>65.85323179999999</v>
       </c>
       <c r="O2">
-        <v>12.578</v>
+        <v>12.512114042</v>
       </c>
       <c r="P2">
-        <v>53.62199999999999</v>
+        <v>53.34111775799999</v>
       </c>
       <c r="Q2">
-        <v>90.72199999999999</v>
+        <v>90.44111775799999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0967720572940558</v>
+        <v>0.09718910139918899</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8664940762838579</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>190.9056251409443</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09662464038519709</v>
+        <v>0.0964772234763384</v>
       </c>
       <c r="C3">
-        <v>678.4170820435822</v>
+        <v>672.7884364354677</v>
       </c>
       <c r="D3">
-        <v>586.2110820435822</v>
+        <v>587.4764364354677</v>
       </c>
       <c r="E3">
-        <v>-102.706</v>
+        <v>-95.812</v>
       </c>
       <c r="F3">
-        <v>6.894</v>
+        <v>13.788</v>
       </c>
       <c r="G3">
         <v>99.09999999999999</v>
@@ -1533,28 +1533,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M3">
-        <v>0.3467682</v>
+        <v>0.6935363999999999</v>
       </c>
       <c r="N3">
-        <v>65.85323179999999</v>
+        <v>65.50646359999999</v>
       </c>
       <c r="O3">
-        <v>12.512114042</v>
+        <v>12.446228084</v>
       </c>
       <c r="P3">
-        <v>53.34111775799999</v>
+        <v>53.06023551599999</v>
       </c>
       <c r="Q3">
-        <v>90.44111775799999</v>
+        <v>90.160235516</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09718910139918899</v>
+        <v>0.09761465660850857</v>
       </c>
       <c r="T3">
-        <v>0.8664940762838579</v>
+        <v>0.8736695484747955</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>190.9056251409443</v>
+        <v>95.45281257047215</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0964772234763384</v>
+        <v>0.09632980656747968</v>
       </c>
       <c r="C4">
-        <v>672.7884364354677</v>
+        <v>667.1652652557024</v>
       </c>
       <c r="D4">
-        <v>587.4764364354677</v>
+        <v>588.7472652557024</v>
       </c>
       <c r="E4">
-        <v>-95.812</v>
+        <v>-88.91799999999999</v>
       </c>
       <c r="F4">
-        <v>13.788</v>
+        <v>20.682</v>
       </c>
       <c r="G4">
         <v>99.09999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M4">
-        <v>0.6935363999999999</v>
+        <v>1.0403046</v>
       </c>
       <c r="N4">
-        <v>65.50646359999999</v>
+        <v>65.15969539999999</v>
       </c>
       <c r="O4">
-        <v>12.446228084</v>
+        <v>12.380342126</v>
       </c>
       <c r="P4">
-        <v>53.06023551599999</v>
+        <v>52.77935327399999</v>
       </c>
       <c r="Q4">
-        <v>90.160235516</v>
+        <v>89.87935327399998</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09761465660850857</v>
+        <v>0.09804898615204091</v>
       </c>
       <c r="T4">
-        <v>0.8736695484747955</v>
+        <v>0.8809929685459584</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>95.45281257047215</v>
+        <v>63.63520838031477</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09632980656747968</v>
+        <v>0.09618238965862098</v>
       </c>
       <c r="C5">
-        <v>667.1652652557024</v>
+        <v>661.5476041081486</v>
       </c>
       <c r="D5">
-        <v>588.7472652557024</v>
+        <v>590.0236041081486</v>
       </c>
       <c r="E5">
-        <v>-88.91799999999999</v>
+        <v>-82.024</v>
       </c>
       <c r="F5">
-        <v>20.682</v>
+        <v>27.576</v>
       </c>
       <c r="G5">
         <v>99.09999999999999</v>
@@ -1697,28 +1697,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M5">
-        <v>1.0403046</v>
+        <v>1.3870728</v>
       </c>
       <c r="N5">
-        <v>65.15969539999999</v>
+        <v>64.81292719999999</v>
       </c>
       <c r="O5">
-        <v>12.380342126</v>
+        <v>12.314456168</v>
       </c>
       <c r="P5">
-        <v>52.77935327399999</v>
+        <v>52.49847103199999</v>
       </c>
       <c r="Q5">
-        <v>89.87935327399998</v>
+        <v>89.59847103199999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09804898615204091</v>
+        <v>0.09849236422773019</v>
       </c>
       <c r="T5">
-        <v>0.8809929685459584</v>
+        <v>0.888468959868604</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>63.63520838031477</v>
+        <v>47.72640628523607</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09618238965862098</v>
+        <v>0.09603497274976228</v>
       </c>
       <c r="C6">
-        <v>661.5476041081486</v>
+        <v>655.9354889060811</v>
       </c>
       <c r="D6">
-        <v>590.0236041081486</v>
+        <v>591.3054889060811</v>
       </c>
       <c r="E6">
-        <v>-82.024</v>
+        <v>-75.13</v>
       </c>
       <c r="F6">
-        <v>27.576</v>
+        <v>34.47</v>
       </c>
       <c r="G6">
         <v>99.09999999999999</v>
@@ -1779,28 +1779,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M6">
-        <v>1.3870728</v>
+        <v>1.733841</v>
       </c>
       <c r="N6">
-        <v>64.81292719999999</v>
+        <v>64.46615899999999</v>
       </c>
       <c r="O6">
-        <v>12.314456168</v>
+        <v>12.24857021</v>
       </c>
       <c r="P6">
-        <v>52.49847103199999</v>
+        <v>52.21758878999999</v>
       </c>
       <c r="Q6">
-        <v>89.59847103199999</v>
+        <v>89.31758879</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09849236422773019</v>
+        <v>0.09894507657869714</v>
       </c>
       <c r="T6">
-        <v>0.888468959868604</v>
+        <v>0.8961023404822527</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.72640628523607</v>
+        <v>38.18112502818885</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09603497274976228</v>
+        <v>0.09588755584090355</v>
       </c>
       <c r="C7">
-        <v>655.9354889060811</v>
+        <v>650.3289558755545</v>
       </c>
       <c r="D7">
-        <v>591.3054889060811</v>
+        <v>592.5929558755545</v>
       </c>
       <c r="E7">
-        <v>-75.13</v>
+        <v>-68.23599999999999</v>
       </c>
       <c r="F7">
-        <v>34.47</v>
+        <v>41.364</v>
       </c>
       <c r="G7">
         <v>99.09999999999999</v>
@@ -1861,28 +1861,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M7">
-        <v>1.733841</v>
+        <v>2.0806092</v>
       </c>
       <c r="N7">
-        <v>64.46615899999999</v>
+        <v>64.11939079999999</v>
       </c>
       <c r="O7">
-        <v>12.24857021</v>
+        <v>12.182684252</v>
       </c>
       <c r="P7">
-        <v>52.21758878999999</v>
+        <v>51.93670654799999</v>
       </c>
       <c r="Q7">
-        <v>89.31758879</v>
+        <v>89.03670654799998</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09894507657869714</v>
+        <v>0.09940742110734421</v>
       </c>
       <c r="T7">
-        <v>0.8961023404822527</v>
+        <v>0.9038981334493832</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.18112502818885</v>
+        <v>31.81760419015738</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09588755584090355</v>
+        <v>0.09574013893204487</v>
       </c>
       <c r="C8">
-        <v>650.3289558755545</v>
+        <v>644.7280415588152</v>
       </c>
       <c r="D8">
-        <v>592.5929558755545</v>
+        <v>593.8860415588152</v>
       </c>
       <c r="E8">
-        <v>-68.23599999999999</v>
+        <v>-61.342</v>
       </c>
       <c r="F8">
-        <v>41.364</v>
+        <v>48.258</v>
       </c>
       <c r="G8">
         <v>99.09999999999999</v>
@@ -1943,28 +1943,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M8">
-        <v>2.0806092</v>
+        <v>2.4273774</v>
       </c>
       <c r="N8">
-        <v>64.11939079999999</v>
+        <v>63.77262259999999</v>
       </c>
       <c r="O8">
-        <v>12.182684252</v>
+        <v>12.116798294</v>
       </c>
       <c r="P8">
-        <v>51.93670654799999</v>
+        <v>51.65582430599999</v>
       </c>
       <c r="Q8">
-        <v>89.03670654799998</v>
+        <v>88.75582430599999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09940742110734421</v>
+        <v>0.0998797085290805</v>
       </c>
       <c r="T8">
-        <v>0.9038981334493832</v>
+        <v>0.9118615778781726</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.81760419015738</v>
+        <v>27.27223216299204</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09574013893204486</v>
+        <v>0.09559272202318617</v>
       </c>
       <c r="C9">
-        <v>644.7280415588153</v>
+        <v>639.1327828177615</v>
       </c>
       <c r="D9">
-        <v>593.8860415588154</v>
+        <v>595.1847828177615</v>
       </c>
       <c r="E9">
-        <v>-61.34199999999999</v>
+        <v>-54.44799999999999</v>
       </c>
       <c r="F9">
-        <v>48.258</v>
+        <v>55.152</v>
       </c>
       <c r="G9">
         <v>99.09999999999999</v>
@@ -2025,28 +2025,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M9">
-        <v>2.4273774</v>
+        <v>2.7741456</v>
       </c>
       <c r="N9">
-        <v>63.77262259999999</v>
+        <v>63.42585439999999</v>
       </c>
       <c r="O9">
-        <v>12.116798294</v>
+        <v>12.050912336</v>
       </c>
       <c r="P9">
-        <v>51.65582430599999</v>
+        <v>51.374942064</v>
       </c>
       <c r="Q9">
-        <v>88.75582430599999</v>
+        <v>88.474942064</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0998797085290805</v>
+        <v>0.1003622630686806</v>
       </c>
       <c r="T9">
-        <v>0.9118615778781726</v>
+        <v>0.9199981406641095</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.27223216299204</v>
+        <v>23.86320314261804</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09559272202318617</v>
+        <v>0.09544530511432746</v>
       </c>
       <c r="C10">
-        <v>639.1327828177615</v>
+        <v>633.5432168374432</v>
       </c>
       <c r="D10">
-        <v>595.1847828177615</v>
+        <v>596.4892168374431</v>
       </c>
       <c r="E10">
-        <v>-54.44799999999999</v>
+        <v>-47.554</v>
       </c>
       <c r="F10">
-        <v>55.152</v>
+        <v>62.04599999999999</v>
       </c>
       <c r="G10">
         <v>99.09999999999999</v>
@@ -2107,28 +2107,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M10">
-        <v>2.7741456</v>
+        <v>3.120913799999999</v>
       </c>
       <c r="N10">
-        <v>63.42585439999999</v>
+        <v>63.07908619999999</v>
       </c>
       <c r="O10">
-        <v>12.050912336</v>
+        <v>11.985026378</v>
       </c>
       <c r="P10">
-        <v>51.374942064</v>
+        <v>51.09405982199999</v>
       </c>
       <c r="Q10">
-        <v>88.474942064</v>
+        <v>88.19405982199999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1003622630686806</v>
+        <v>0.1008554232025576</v>
       </c>
       <c r="T10">
-        <v>0.9199981406641095</v>
+        <v>0.928313529005781</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.86320314261804</v>
+        <v>21.21173612677159</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09544530511432746</v>
+        <v>0.09529788820546876</v>
       </c>
       <c r="C11">
-        <v>633.5432168374432</v>
+        <v>627.9593811296118</v>
       </c>
       <c r="D11">
-        <v>596.4892168374431</v>
+        <v>597.7993811296117</v>
       </c>
       <c r="E11">
-        <v>-47.554</v>
+        <v>-40.66</v>
       </c>
       <c r="F11">
-        <v>62.04599999999999</v>
+        <v>68.94</v>
       </c>
       <c r="G11">
         <v>99.09999999999999</v>
@@ -2189,28 +2189,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M11">
-        <v>3.120913799999999</v>
+        <v>3.467682</v>
       </c>
       <c r="N11">
-        <v>63.07908619999999</v>
+        <v>62.73231799999999</v>
       </c>
       <c r="O11">
-        <v>11.985026378</v>
+        <v>11.91914042</v>
       </c>
       <c r="P11">
-        <v>51.09405982199999</v>
+        <v>50.81317757999999</v>
       </c>
       <c r="Q11">
-        <v>88.19405982199999</v>
+        <v>87.91317758</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1008554232025576</v>
+        <v>0.1013595424505208</v>
       </c>
       <c r="T11">
-        <v>0.928313529005781</v>
+        <v>0.9368137037550457</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.21173612677159</v>
+        <v>19.09056251409443</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09529788820546876</v>
+        <v>0.09515047129661004</v>
       </c>
       <c r="C12">
-        <v>627.9593811296118</v>
+        <v>622.3813135363173</v>
       </c>
       <c r="D12">
-        <v>597.7993811296117</v>
+        <v>599.1153135363173</v>
       </c>
       <c r="E12">
-        <v>-40.66</v>
+        <v>-33.76599999999999</v>
       </c>
       <c r="F12">
-        <v>68.94</v>
+        <v>75.834</v>
       </c>
       <c r="G12">
         <v>99.09999999999999</v>
@@ -2271,28 +2271,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M12">
-        <v>3.467682</v>
+        <v>3.8144502</v>
       </c>
       <c r="N12">
-        <v>62.73231799999999</v>
+        <v>62.38554979999999</v>
       </c>
       <c r="O12">
-        <v>11.91914042</v>
+        <v>11.853254462</v>
       </c>
       <c r="P12">
-        <v>50.81317757999999</v>
+        <v>50.53229533799999</v>
       </c>
       <c r="Q12">
-        <v>87.91317758</v>
+        <v>87.63229533799999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1013595424505208</v>
+        <v>0.1018749902209101</v>
       </c>
       <c r="T12">
-        <v>0.9368137037550457</v>
+        <v>0.9455048936672148</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.09056251409443</v>
+        <v>17.35505683099493</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09515047129661004</v>
+        <v>0.09500305438775133</v>
       </c>
       <c r="C13">
-        <v>622.3813135363173</v>
+        <v>616.8090522335502</v>
       </c>
       <c r="D13">
-        <v>599.1153135363173</v>
+        <v>600.4370522335502</v>
       </c>
       <c r="E13">
-        <v>-33.76599999999999</v>
+        <v>-26.872</v>
       </c>
       <c r="F13">
-        <v>75.834</v>
+        <v>82.72799999999999</v>
       </c>
       <c r="G13">
         <v>99.09999999999999</v>
@@ -2353,28 +2353,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M13">
-        <v>3.8144502</v>
+        <v>4.161218399999999</v>
       </c>
       <c r="N13">
-        <v>62.38554979999999</v>
+        <v>62.03878159999999</v>
       </c>
       <c r="O13">
-        <v>11.853254462</v>
+        <v>11.787368504</v>
       </c>
       <c r="P13">
-        <v>50.53229533799999</v>
+        <v>50.25141309599999</v>
       </c>
       <c r="Q13">
-        <v>87.63229533799999</v>
+        <v>87.35141309599999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1018749902209101</v>
+        <v>0.1024021527133538</v>
       </c>
       <c r="T13">
-        <v>0.9455048936672148</v>
+        <v>0.9543936106228424</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.35505683099493</v>
+        <v>15.90880209507869</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09500305438775133</v>
+        <v>0.09485563747889263</v>
       </c>
       <c r="C14">
-        <v>616.8090522335502</v>
+        <v>611.2426357349339</v>
       </c>
       <c r="D14">
-        <v>600.4370522335502</v>
+        <v>601.7646357349338</v>
       </c>
       <c r="E14">
-        <v>-26.872</v>
+        <v>-19.97799999999999</v>
       </c>
       <c r="F14">
-        <v>82.72799999999999</v>
+        <v>89.622</v>
       </c>
       <c r="G14">
         <v>99.09999999999999</v>
@@ -2435,28 +2435,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M14">
-        <v>4.161218399999999</v>
+        <v>4.5079866</v>
       </c>
       <c r="N14">
-        <v>62.03878159999999</v>
+        <v>61.69201339999999</v>
       </c>
       <c r="O14">
-        <v>11.787368504</v>
+        <v>11.721482546</v>
       </c>
       <c r="P14">
-        <v>50.25141309599999</v>
+        <v>49.97053085399999</v>
       </c>
       <c r="Q14">
-        <v>87.35141309599999</v>
+        <v>87.070530854</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1024021527133538</v>
+        <v>0.1029414338837846</v>
       </c>
       <c r="T14">
-        <v>0.9543936106228424</v>
+        <v>0.9634866658992892</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.90880209507869</v>
+        <v>14.68504808776494</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09485563747889263</v>
+        <v>0.09470822057003393</v>
       </c>
       <c r="C15">
-        <v>611.2426357349339</v>
+        <v>605.6821028954653</v>
       </c>
       <c r="D15">
-        <v>601.7646357349338</v>
+        <v>603.0981028954652</v>
       </c>
       <c r="E15">
-        <v>-19.97799999999999</v>
+        <v>-13.08399999999999</v>
       </c>
       <c r="F15">
-        <v>89.622</v>
+        <v>96.51600000000001</v>
       </c>
       <c r="G15">
         <v>99.09999999999999</v>
@@ -2517,28 +2517,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M15">
-        <v>4.5079866</v>
+        <v>4.8547548</v>
       </c>
       <c r="N15">
-        <v>61.69201339999999</v>
+        <v>61.34524519999999</v>
       </c>
       <c r="O15">
-        <v>11.721482546</v>
+        <v>11.655596588</v>
       </c>
       <c r="P15">
-        <v>49.97053085399999</v>
+        <v>49.68964861199998</v>
       </c>
       <c r="Q15">
-        <v>87.070530854</v>
+        <v>86.78964861199998</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1029414338837846</v>
+        <v>0.1034932564767836</v>
       </c>
       <c r="T15">
-        <v>0.9634866658992892</v>
+        <v>0.9727911875775138</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.68504808776494</v>
+        <v>13.63611608149602</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09470822057003393</v>
+        <v>0.09474305366117522</v>
       </c>
       <c r="C16">
-        <v>605.6821028954653</v>
+        <v>598.47248544765</v>
       </c>
       <c r="D16">
-        <v>603.0981028954652</v>
+        <v>602.7824854476499</v>
       </c>
       <c r="E16">
-        <v>-13.08399999999999</v>
+        <v>-6.189999999999984</v>
       </c>
       <c r="F16">
-        <v>96.51600000000001</v>
+        <v>103.41</v>
       </c>
       <c r="G16">
         <v>99.09999999999999</v>
@@ -2599,45 +2599,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M16">
-        <v>4.8547548</v>
+        <v>5.356638</v>
       </c>
       <c r="N16">
-        <v>61.34524519999999</v>
+        <v>60.84336199999998</v>
       </c>
       <c r="O16">
-        <v>11.655596588</v>
+        <v>11.56023878</v>
       </c>
       <c r="P16">
-        <v>49.68964861199998</v>
+        <v>49.28312321999999</v>
       </c>
       <c r="Q16">
-        <v>86.78964861199998</v>
+        <v>86.38312321999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1034932564767836</v>
+        <v>0.1040580631307944</v>
       </c>
       <c r="T16">
-        <v>0.9727911875775138</v>
+        <v>0.9823146391775789</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.19</v>
       </c>
       <c r="W16">
-        <v>0.040743</v>
+        <v>0.041958</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.63611608149602</v>
+        <v>12.35849799818468</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09474305366117522</v>
+        <v>0.09460778675231651</v>
       </c>
       <c r="C17">
-        <v>598.47248544765</v>
+        <v>592.8059718769704</v>
       </c>
       <c r="D17">
-        <v>602.7824854476499</v>
+        <v>604.0099718769703</v>
       </c>
       <c r="E17">
-        <v>-6.189999999999998</v>
+        <v>0.7040000000000077</v>
       </c>
       <c r="F17">
-        <v>103.41</v>
+        <v>110.304</v>
       </c>
       <c r="G17">
         <v>99.09999999999999</v>
@@ -2681,28 +2681,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M17">
-        <v>5.356637999999999</v>
+        <v>5.7137472</v>
       </c>
       <c r="N17">
-        <v>60.84336199999999</v>
+        <v>60.48625279999999</v>
       </c>
       <c r="O17">
-        <v>11.56023878</v>
+        <v>11.492388032</v>
       </c>
       <c r="P17">
-        <v>49.28312321999999</v>
+        <v>48.99386476799999</v>
       </c>
       <c r="Q17">
-        <v>86.38312321999999</v>
+        <v>86.093864768</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1040580631307944</v>
+        <v>0.1046363175622816</v>
       </c>
       <c r="T17">
-        <v>0.9823146391775789</v>
+        <v>0.9920648396252646</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.35849799818468</v>
+        <v>11.58609187329814</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09460778675231651</v>
+        <v>0.09447251984345781</v>
       </c>
       <c r="C18">
-        <v>592.8059718769704</v>
+        <v>587.1444677333145</v>
       </c>
       <c r="D18">
-        <v>604.0099718769703</v>
+        <v>605.2424677333145</v>
       </c>
       <c r="E18">
-        <v>0.7040000000000077</v>
+        <v>7.598000000000013</v>
       </c>
       <c r="F18">
-        <v>110.304</v>
+        <v>117.198</v>
       </c>
       <c r="G18">
         <v>99.09999999999999</v>
@@ -2763,28 +2763,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M18">
-        <v>5.7137472</v>
+        <v>6.0708564</v>
       </c>
       <c r="N18">
-        <v>60.48625279999999</v>
+        <v>60.12914359999999</v>
       </c>
       <c r="O18">
-        <v>11.492388032</v>
+        <v>11.424537284</v>
       </c>
       <c r="P18">
-        <v>48.99386476799999</v>
+        <v>48.704606316</v>
       </c>
       <c r="Q18">
-        <v>86.093864768</v>
+        <v>85.80460631599999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1046363175622816</v>
+        <v>0.1052285058354913</v>
       </c>
       <c r="T18">
-        <v>0.9920648396252646</v>
+        <v>1.002049984662051</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.58609187329814</v>
+        <v>10.90455705722178</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09447251984345781</v>
+        <v>0.0943372529345991</v>
       </c>
       <c r="C19">
-        <v>587.1444677333145</v>
+        <v>581.4880037449276</v>
       </c>
       <c r="D19">
-        <v>605.2424677333145</v>
+        <v>606.4800037449276</v>
       </c>
       <c r="E19">
-        <v>7.598000000000013</v>
+        <v>14.49200000000002</v>
       </c>
       <c r="F19">
-        <v>117.198</v>
+        <v>124.092</v>
       </c>
       <c r="G19">
         <v>99.09999999999999</v>
@@ -2845,28 +2845,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M19">
-        <v>6.0708564</v>
+        <v>6.4279656</v>
       </c>
       <c r="N19">
-        <v>60.12914359999999</v>
+        <v>59.77203439999999</v>
       </c>
       <c r="O19">
-        <v>11.424537284</v>
+        <v>11.356686536</v>
       </c>
       <c r="P19">
-        <v>48.704606316</v>
+        <v>48.41534786399999</v>
       </c>
       <c r="Q19">
-        <v>85.80460631599999</v>
+        <v>85.51534786399999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1052285058354913</v>
+        <v>0.1058351377251208</v>
       </c>
       <c r="T19">
-        <v>1.002049984662051</v>
+        <v>1.012278669821686</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.90455705722178</v>
+        <v>10.29874833182057</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0943372529345991</v>
+        <v>0.09446361602574038</v>
       </c>
       <c r="C20">
-        <v>581.4880037449276</v>
+        <v>573.4377720836121</v>
       </c>
       <c r="D20">
-        <v>606.4800037449276</v>
+        <v>605.3237720836121</v>
       </c>
       <c r="E20">
-        <v>14.49199999999999</v>
+        <v>21.386</v>
       </c>
       <c r="F20">
-        <v>124.092</v>
+        <v>130.986</v>
       </c>
       <c r="G20">
         <v>99.09999999999999</v>
@@ -2927,45 +2927,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M20">
-        <v>6.427965599999999</v>
+        <v>7.007750999999999</v>
       </c>
       <c r="N20">
-        <v>59.77203439999999</v>
+        <v>59.19224899999999</v>
       </c>
       <c r="O20">
-        <v>11.356686536</v>
+        <v>11.24652731</v>
       </c>
       <c r="P20">
-        <v>48.41534786399999</v>
+        <v>47.94572168999999</v>
       </c>
       <c r="Q20">
-        <v>85.51534786399999</v>
+        <v>85.04572168999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1058351377251208</v>
+        <v>0.1064567481799264</v>
       </c>
       <c r="T20">
-        <v>1.012278669821686</v>
+        <v>1.022759915108719</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.19</v>
       </c>
       <c r="W20">
-        <v>0.041958</v>
+        <v>0.04333500000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.29874833182057</v>
+        <v>9.4466826803635</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09446361602574038</v>
+        <v>0.0943421191168817</v>
       </c>
       <c r="C21">
-        <v>573.4377720836121</v>
+        <v>567.6553960479641</v>
       </c>
       <c r="D21">
-        <v>605.3237720836121</v>
+        <v>606.4353960479641</v>
       </c>
       <c r="E21">
-        <v>21.386</v>
+        <v>28.28</v>
       </c>
       <c r="F21">
-        <v>130.986</v>
+        <v>137.88</v>
       </c>
       <c r="G21">
         <v>99.09999999999999</v>
@@ -3009,28 +3009,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M21">
-        <v>7.007750999999999</v>
+        <v>7.37658</v>
       </c>
       <c r="N21">
-        <v>59.19224899999999</v>
+        <v>58.82341999999999</v>
       </c>
       <c r="O21">
-        <v>11.24652731</v>
+        <v>11.1764498</v>
       </c>
       <c r="P21">
-        <v>47.94572168999999</v>
+        <v>47.64697019999999</v>
       </c>
       <c r="Q21">
-        <v>85.04572168999999</v>
+        <v>84.74697019999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1064567481799264</v>
+        <v>0.1070938988961021</v>
       </c>
       <c r="T21">
-        <v>1.022759915108719</v>
+        <v>1.033503191527929</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.4466826803635</v>
+        <v>8.974348546345325</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0943421191168817</v>
+        <v>0.09422062220802299</v>
       </c>
       <c r="C22">
-        <v>567.6553960479641</v>
+        <v>561.8771103234495</v>
       </c>
       <c r="D22">
-        <v>606.4353960479641</v>
+        <v>607.5511103234495</v>
       </c>
       <c r="E22">
-        <v>28.28</v>
+        <v>35.17400000000001</v>
       </c>
       <c r="F22">
-        <v>137.88</v>
+        <v>144.774</v>
       </c>
       <c r="G22">
         <v>99.09999999999999</v>
@@ -3091,28 +3091,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M22">
-        <v>7.37658</v>
+        <v>7.745409</v>
       </c>
       <c r="N22">
-        <v>58.82341999999999</v>
+        <v>58.45459099999999</v>
       </c>
       <c r="O22">
-        <v>11.1764498</v>
+        <v>11.10637229</v>
       </c>
       <c r="P22">
-        <v>47.64697019999999</v>
+        <v>47.34821870999999</v>
       </c>
       <c r="Q22">
-        <v>84.74697019999999</v>
+        <v>84.44821870999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1070938988961021</v>
+        <v>0.1077471800101557</v>
       </c>
       <c r="T22">
-        <v>1.033503191527929</v>
+        <v>1.044518449628637</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.974348546345325</v>
+        <v>8.546998615566975</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09422062220802299</v>
+        <v>0.09409912529916427</v>
       </c>
       <c r="C23">
-        <v>561.8771103234495</v>
+        <v>556.1029375276305</v>
       </c>
       <c r="D23">
-        <v>607.5511103234495</v>
+        <v>608.6709375276305</v>
       </c>
       <c r="E23">
-        <v>35.17400000000001</v>
+        <v>42.06800000000001</v>
       </c>
       <c r="F23">
-        <v>144.774</v>
+        <v>151.668</v>
       </c>
       <c r="G23">
         <v>99.09999999999999</v>
@@ -3173,28 +3173,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M23">
-        <v>7.745409</v>
+        <v>8.114238</v>
       </c>
       <c r="N23">
-        <v>58.45459099999999</v>
+        <v>58.08576199999999</v>
       </c>
       <c r="O23">
-        <v>11.10637229</v>
+        <v>11.03629478</v>
       </c>
       <c r="P23">
-        <v>47.34821870999999</v>
+        <v>47.04946721999999</v>
       </c>
       <c r="Q23">
-        <v>84.44821870999999</v>
+        <v>84.14946721999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1077471800101557</v>
+        <v>0.1084172119220055</v>
       </c>
       <c r="T23">
-        <v>1.044518449628637</v>
+        <v>1.055816150244748</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.546998615566975</v>
+        <v>8.158498678495748</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09409912529916427</v>
+        <v>0.09397762839030557</v>
       </c>
       <c r="C24">
-        <v>556.1029375276305</v>
+        <v>550.3329004451299</v>
       </c>
       <c r="D24">
-        <v>608.6709375276305</v>
+        <v>609.7949004451299</v>
       </c>
       <c r="E24">
-        <v>42.06800000000001</v>
+        <v>48.96200000000002</v>
       </c>
       <c r="F24">
-        <v>151.668</v>
+        <v>158.562</v>
       </c>
       <c r="G24">
         <v>99.09999999999999</v>
@@ -3255,28 +3255,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M24">
-        <v>8.114238</v>
+        <v>8.483067</v>
       </c>
       <c r="N24">
-        <v>58.08576199999999</v>
+        <v>57.71693299999999</v>
       </c>
       <c r="O24">
-        <v>11.03629478</v>
+        <v>10.96621727</v>
       </c>
       <c r="P24">
-        <v>47.04946721999999</v>
+        <v>46.75071573</v>
       </c>
       <c r="Q24">
-        <v>84.14946721999999</v>
+        <v>83.85071572999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1084172119220055</v>
+        <v>0.1091046472601371</v>
       </c>
       <c r="T24">
-        <v>1.055816150244748</v>
+        <v>1.067407297630109</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.158498678495748</v>
+        <v>7.803781344648108</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09397762839030557</v>
+        <v>0.09401165148144686</v>
       </c>
       <c r="C25">
-        <v>550.3329004451299</v>
+        <v>543.123735992344</v>
       </c>
       <c r="D25">
-        <v>609.7949004451299</v>
+        <v>609.479735992344</v>
       </c>
       <c r="E25">
-        <v>48.96200000000002</v>
+        <v>55.85600000000002</v>
       </c>
       <c r="F25">
-        <v>158.562</v>
+        <v>165.456</v>
       </c>
       <c r="G25">
         <v>99.09999999999999</v>
@@ -3337,45 +3337,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M25">
-        <v>8.483067</v>
+        <v>8.984260800000001</v>
       </c>
       <c r="N25">
-        <v>57.71693299999999</v>
+        <v>57.21573919999999</v>
       </c>
       <c r="O25">
-        <v>10.96621727</v>
+        <v>10.870990448</v>
       </c>
       <c r="P25">
-        <v>46.75071573</v>
+        <v>46.34474875199999</v>
       </c>
       <c r="Q25">
-        <v>83.85071572999999</v>
+        <v>83.44474875199998</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1091046472601371</v>
+        <v>0.1098101730019038</v>
       </c>
       <c r="T25">
-        <v>1.067407297630109</v>
+        <v>1.079303475209821</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.19</v>
       </c>
       <c r="W25">
-        <v>0.04333500000000001</v>
+        <v>0.043983</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.803781344648108</v>
+        <v>7.368441486026316</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09401165148144686</v>
+        <v>0.09389663457258816</v>
       </c>
       <c r="C26">
-        <v>543.123735992344</v>
+        <v>537.2964797105938</v>
       </c>
       <c r="D26">
-        <v>609.479735992344</v>
+        <v>610.5464797105938</v>
       </c>
       <c r="E26">
-        <v>55.85599999999999</v>
+        <v>62.75</v>
       </c>
       <c r="F26">
-        <v>165.456</v>
+        <v>172.35</v>
       </c>
       <c r="G26">
         <v>99.09999999999999</v>
@@ -3419,28 +3419,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M26">
-        <v>8.984260799999999</v>
+        <v>9.358605000000001</v>
       </c>
       <c r="N26">
-        <v>57.21573919999999</v>
+        <v>56.84139499999999</v>
       </c>
       <c r="O26">
-        <v>10.870990448</v>
+        <v>10.79986505</v>
       </c>
       <c r="P26">
-        <v>46.34474875199999</v>
+        <v>46.04152994999999</v>
       </c>
       <c r="Q26">
-        <v>83.44474875199998</v>
+        <v>83.14152994999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1098101730019038</v>
+        <v>0.1105345127634509</v>
       </c>
       <c r="T26">
-        <v>1.079303475209821</v>
+        <v>1.091516884191659</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.368441486026318</v>
+        <v>7.073703826585264</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09389663457258816</v>
+        <v>0.09378161766372944</v>
       </c>
       <c r="C27">
-        <v>537.2964797105938</v>
+        <v>531.4729641187199</v>
       </c>
       <c r="D27">
-        <v>610.5464797105938</v>
+        <v>611.6169641187199</v>
       </c>
       <c r="E27">
-        <v>62.75</v>
+        <v>69.64400000000001</v>
       </c>
       <c r="F27">
-        <v>172.35</v>
+        <v>179.244</v>
       </c>
       <c r="G27">
         <v>99.09999999999999</v>
@@ -3501,28 +3501,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M27">
-        <v>9.358605000000001</v>
+        <v>9.7329492</v>
       </c>
       <c r="N27">
-        <v>56.84139499999999</v>
+        <v>56.46705079999999</v>
       </c>
       <c r="O27">
-        <v>10.79986505</v>
+        <v>10.728739652</v>
       </c>
       <c r="P27">
-        <v>46.04152994999999</v>
+        <v>45.73831114799999</v>
       </c>
       <c r="Q27">
-        <v>83.14152994999999</v>
+        <v>82.838311148</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1105345127634509</v>
+        <v>0.1112784292753101</v>
       </c>
       <c r="T27">
-        <v>1.091516884191659</v>
+        <v>1.104060385308141</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.073703826585264</v>
+        <v>6.801638294793523</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09378161766372944</v>
+        <v>0.09366660075487074</v>
       </c>
       <c r="C28">
-        <v>531.4729641187199</v>
+        <v>525.6532089271797</v>
       </c>
       <c r="D28">
-        <v>611.6169641187199</v>
+        <v>612.6912089271797</v>
       </c>
       <c r="E28">
-        <v>69.64400000000001</v>
+        <v>76.53800000000001</v>
       </c>
       <c r="F28">
-        <v>179.244</v>
+        <v>186.138</v>
       </c>
       <c r="G28">
         <v>99.09999999999999</v>
@@ -3583,28 +3583,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M28">
-        <v>9.7329492</v>
+        <v>10.1072934</v>
       </c>
       <c r="N28">
-        <v>56.46705079999999</v>
+        <v>56.09270659999999</v>
       </c>
       <c r="O28">
-        <v>10.728739652</v>
+        <v>10.657614254</v>
       </c>
       <c r="P28">
-        <v>45.73831114799999</v>
+        <v>45.43509234599999</v>
       </c>
       <c r="Q28">
-        <v>82.838311148</v>
+        <v>82.535092346</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1112784292753101</v>
+        <v>0.1120427270614668</v>
       </c>
       <c r="T28">
-        <v>1.104060385308141</v>
+        <v>1.116947543989458</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.801638294793523</v>
+        <v>6.549725765356726</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09366660075487074</v>
+        <v>0.09355158384601205</v>
       </c>
       <c r="C29">
-        <v>525.6532089271797</v>
+        <v>519.8372339851517</v>
       </c>
       <c r="D29">
-        <v>612.6912089271797</v>
+        <v>613.7692339851517</v>
       </c>
       <c r="E29">
-        <v>76.53800000000001</v>
+        <v>83.43200000000002</v>
       </c>
       <c r="F29">
-        <v>186.138</v>
+        <v>193.032</v>
       </c>
       <c r="G29">
         <v>99.09999999999999</v>
@@ -3665,28 +3665,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M29">
-        <v>10.1072934</v>
+        <v>10.4816376</v>
       </c>
       <c r="N29">
-        <v>56.09270659999999</v>
+        <v>55.71836239999999</v>
       </c>
       <c r="O29">
-        <v>10.657614254</v>
+        <v>10.586488856</v>
       </c>
       <c r="P29">
-        <v>45.43509234599999</v>
+        <v>45.13187354399999</v>
       </c>
       <c r="Q29">
-        <v>82.535092346</v>
+        <v>82.231873544</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1120427270614668</v>
+        <v>0.1128282553416834</v>
       </c>
       <c r="T29">
-        <v>1.116947543989458</v>
+        <v>1.130192679300812</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.549725765356726</v>
+        <v>6.315806988022557</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09355158384601205</v>
+        <v>0.09367146693715332</v>
       </c>
       <c r="C30">
-        <v>519.8372339851517</v>
+        <v>511.8196828951098</v>
       </c>
       <c r="D30">
-        <v>613.7692339851517</v>
+        <v>612.6456828951099</v>
       </c>
       <c r="E30">
-        <v>83.43200000000002</v>
+        <v>90.32600000000002</v>
       </c>
       <c r="F30">
-        <v>193.032</v>
+        <v>199.926</v>
       </c>
       <c r="G30">
         <v>99.09999999999999</v>
@@ -3747,45 +3747,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M30">
-        <v>10.4816376</v>
+        <v>11.0559078</v>
       </c>
       <c r="N30">
-        <v>55.71836239999999</v>
+        <v>55.14409219999999</v>
       </c>
       <c r="O30">
-        <v>10.586488856</v>
+        <v>10.477377518</v>
       </c>
       <c r="P30">
-        <v>45.13187354399999</v>
+        <v>44.66671468199999</v>
       </c>
       <c r="Q30">
-        <v>82.231873544</v>
+        <v>81.76671468199999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1128282553416834</v>
+        <v>0.1136359111790892</v>
       </c>
       <c r="T30">
-        <v>1.130192679300812</v>
+        <v>1.143810917015303</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.19</v>
       </c>
       <c r="W30">
-        <v>0.043983</v>
+        <v>0.04479300000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.315806988022557</v>
+        <v>5.987748920988648</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09367146693715332</v>
+        <v>0.09356455002829463</v>
       </c>
       <c r="C31">
-        <v>511.8196828951099</v>
+        <v>505.9275154776946</v>
       </c>
       <c r="D31">
-        <v>612.6456828951099</v>
+        <v>613.6475154776946</v>
       </c>
       <c r="E31">
-        <v>90.32599999999999</v>
+        <v>97.22</v>
       </c>
       <c r="F31">
-        <v>199.926</v>
+        <v>206.82</v>
       </c>
       <c r="G31">
         <v>99.09999999999999</v>
@@ -3829,28 +3829,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M31">
-        <v>11.0559078</v>
+        <v>11.437146</v>
       </c>
       <c r="N31">
-        <v>55.14409219999999</v>
+        <v>54.76285399999999</v>
       </c>
       <c r="O31">
-        <v>10.477377518</v>
+        <v>10.40494226</v>
       </c>
       <c r="P31">
-        <v>44.66671468199999</v>
+        <v>44.35791173999999</v>
       </c>
       <c r="Q31">
-        <v>81.76671468199999</v>
+        <v>81.45791173999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1136359111790892</v>
+        <v>0.1144666428975638</v>
       </c>
       <c r="T31">
-        <v>1.143810917015302</v>
+        <v>1.157818247235921</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.987748920988649</v>
+        <v>5.788157290289027</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09356455002829463</v>
+        <v>0.09345763311943592</v>
       </c>
       <c r="C32">
-        <v>505.9275154776946</v>
+        <v>500.0386299326403</v>
       </c>
       <c r="D32">
-        <v>613.6475154776946</v>
+        <v>614.6526299326403</v>
       </c>
       <c r="E32">
-        <v>97.22</v>
+        <v>104.114</v>
       </c>
       <c r="F32">
-        <v>206.82</v>
+        <v>213.714</v>
       </c>
       <c r="G32">
         <v>99.09999999999999</v>
@@ -3911,28 +3911,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M32">
-        <v>11.437146</v>
+        <v>11.8183842</v>
       </c>
       <c r="N32">
-        <v>54.76285399999999</v>
+        <v>54.38161579999999</v>
       </c>
       <c r="O32">
-        <v>10.40494226</v>
+        <v>10.332507002</v>
       </c>
       <c r="P32">
-        <v>44.35791173999999</v>
+        <v>44.04910879799999</v>
       </c>
       <c r="Q32">
-        <v>81.45791173999999</v>
+        <v>81.14910879799999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1144666428975638</v>
+        <v>0.1153214537962839</v>
       </c>
       <c r="T32">
-        <v>1.157818247235921</v>
+        <v>1.172231587028152</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.788157290289027</v>
+        <v>5.601442538989382</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09345763311943592</v>
+        <v>0.09335071621057721</v>
       </c>
       <c r="C33">
-        <v>500.0386299326403</v>
+        <v>494.1530424128806</v>
       </c>
       <c r="D33">
-        <v>614.6526299326403</v>
+        <v>615.6610424128805</v>
       </c>
       <c r="E33">
-        <v>104.114</v>
+        <v>111.008</v>
       </c>
       <c r="F33">
-        <v>213.714</v>
+        <v>220.608</v>
       </c>
       <c r="G33">
         <v>99.09999999999999</v>
@@ -3993,28 +3993,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M33">
-        <v>11.8183842</v>
+        <v>12.1996224</v>
       </c>
       <c r="N33">
-        <v>54.38161579999999</v>
+        <v>54.00037759999999</v>
       </c>
       <c r="O33">
-        <v>10.332507002</v>
+        <v>10.260071744</v>
       </c>
       <c r="P33">
-        <v>44.04910879799999</v>
+        <v>43.74030585599999</v>
       </c>
       <c r="Q33">
-        <v>81.14910879799999</v>
+        <v>80.84030585599999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1153214537962839</v>
+        <v>0.1162014061920253</v>
       </c>
       <c r="T33">
-        <v>1.172231587028152</v>
+        <v>1.187068848578979</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.601442538989382</v>
+        <v>5.426397459645963</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09335071621057721</v>
+        <v>0.0932437993017185</v>
       </c>
       <c r="C34">
-        <v>494.1530424128806</v>
+        <v>488.2707691775267</v>
       </c>
       <c r="D34">
-        <v>615.6610424128805</v>
+        <v>616.6727691775267</v>
       </c>
       <c r="E34">
-        <v>111.008</v>
+        <v>117.902</v>
       </c>
       <c r="F34">
-        <v>220.608</v>
+        <v>227.502</v>
       </c>
       <c r="G34">
         <v>99.09999999999999</v>
@@ -4075,28 +4075,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M34">
-        <v>12.1996224</v>
+        <v>12.5808606</v>
       </c>
       <c r="N34">
-        <v>54.00037759999999</v>
+        <v>53.61913939999999</v>
       </c>
       <c r="O34">
-        <v>10.260071744</v>
+        <v>10.187636486</v>
       </c>
       <c r="P34">
-        <v>43.74030585599999</v>
+        <v>43.43150291399999</v>
       </c>
       <c r="Q34">
-        <v>80.84030585599999</v>
+        <v>80.53150291399999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1162014061920253</v>
+        <v>0.1171076258234605</v>
       </c>
       <c r="T34">
-        <v>1.187068848578979</v>
+        <v>1.20234901345968</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.426397459645963</v>
+        <v>5.261961172990024</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0932437993017185</v>
+        <v>0.0931368823928598</v>
       </c>
       <c r="C35">
-        <v>488.2707691775267</v>
+        <v>482.3918265927412</v>
       </c>
       <c r="D35">
-        <v>616.6727691775267</v>
+        <v>617.6878265927412</v>
       </c>
       <c r="E35">
-        <v>117.902</v>
+        <v>124.796</v>
       </c>
       <c r="F35">
-        <v>227.502</v>
+        <v>234.396</v>
       </c>
       <c r="G35">
         <v>99.09999999999999</v>
@@ -4157,28 +4157,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M35">
-        <v>12.5808606</v>
+        <v>12.9620988</v>
       </c>
       <c r="N35">
-        <v>53.61913939999999</v>
+        <v>53.23790119999999</v>
       </c>
       <c r="O35">
-        <v>10.187636486</v>
+        <v>10.115201228</v>
       </c>
       <c r="P35">
-        <v>43.43150291399999</v>
+        <v>43.12269997199999</v>
       </c>
       <c r="Q35">
-        <v>80.53150291399999</v>
+        <v>80.22269997199999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1171076258234605</v>
+        <v>0.1180413066558482</v>
       </c>
       <c r="T35">
-        <v>1.20234901345968</v>
+        <v>1.218092213639797</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.261961172990024</v>
+        <v>5.107197609078553</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0931368823928598</v>
+        <v>0.09302996548400108</v>
       </c>
       <c r="C36">
-        <v>482.3918265927412</v>
+        <v>476.5162311326213</v>
       </c>
       <c r="D36">
-        <v>617.6878265927412</v>
+        <v>618.7062311326213</v>
       </c>
       <c r="E36">
-        <v>124.796</v>
+        <v>131.69</v>
       </c>
       <c r="F36">
-        <v>234.396</v>
+        <v>241.29</v>
       </c>
       <c r="G36">
         <v>99.09999999999999</v>
@@ -4239,28 +4239,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M36">
-        <v>12.9620988</v>
+        <v>13.343337</v>
       </c>
       <c r="N36">
-        <v>53.23790119999999</v>
+        <v>52.85666299999998</v>
       </c>
       <c r="O36">
-        <v>10.115201228</v>
+        <v>10.04276597</v>
       </c>
       <c r="P36">
-        <v>43.12269997199999</v>
+        <v>42.81389702999999</v>
       </c>
       <c r="Q36">
-        <v>80.22269997199999</v>
+        <v>79.91389702999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1180413066558482</v>
+        <v>0.1190037161292324</v>
       </c>
       <c r="T36">
-        <v>1.218092213639797</v>
+        <v>1.234319819979301</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.107197609078553</v>
+        <v>4.961277677390594</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09302996548400108</v>
+        <v>0.09292304857514239</v>
       </c>
       <c r="C37">
-        <v>476.5162311326213</v>
+        <v>470.643999380088</v>
       </c>
       <c r="D37">
-        <v>618.7062311326213</v>
+        <v>619.727999380088</v>
       </c>
       <c r="E37">
-        <v>131.69</v>
+        <v>138.584</v>
       </c>
       <c r="F37">
-        <v>241.29</v>
+        <v>248.184</v>
       </c>
       <c r="G37">
         <v>99.09999999999999</v>
@@ -4321,28 +4321,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M37">
-        <v>13.343337</v>
+        <v>13.7245752</v>
       </c>
       <c r="N37">
-        <v>52.85666299999998</v>
+        <v>52.47542479999998</v>
       </c>
       <c r="O37">
-        <v>10.04276597</v>
+        <v>9.970330711999997</v>
       </c>
       <c r="P37">
-        <v>42.81389702999999</v>
+        <v>42.50509408799999</v>
       </c>
       <c r="Q37">
-        <v>79.91389702999999</v>
+        <v>79.60509408799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1190037161292324</v>
+        <v>0.11999620089866</v>
       </c>
       <c r="T37">
-        <v>1.234319819979301</v>
+        <v>1.251054539016916</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.961277677390594</v>
+        <v>4.823464408574189</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09292304857514239</v>
+        <v>0.09281613166628369</v>
       </c>
       <c r="C38">
-        <v>470.6439993800881</v>
+        <v>464.7751480277891</v>
       </c>
       <c r="D38">
-        <v>619.727999380088</v>
+        <v>620.7531480277891</v>
       </c>
       <c r="E38">
-        <v>138.584</v>
+        <v>145.478</v>
       </c>
       <c r="F38">
-        <v>248.184</v>
+        <v>255.078</v>
       </c>
       <c r="G38">
         <v>99.09999999999999</v>
@@ -4403,28 +4403,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M38">
-        <v>13.7245752</v>
+        <v>14.1058134</v>
       </c>
       <c r="N38">
-        <v>52.47542479999999</v>
+        <v>52.09418659999999</v>
       </c>
       <c r="O38">
-        <v>9.970330711999999</v>
+        <v>9.897895453999997</v>
       </c>
       <c r="P38">
-        <v>42.50509408799999</v>
+        <v>42.19629114599999</v>
       </c>
       <c r="Q38">
-        <v>79.60509408799999</v>
+        <v>79.29629114599999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.11999620089866</v>
+        <v>0.1210201931210852</v>
       </c>
       <c r="T38">
-        <v>1.251054539016916</v>
+        <v>1.268320518976359</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.82346440857419</v>
+        <v>4.693100505639752</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09281613166628369</v>
+        <v>0.09270921475742497</v>
       </c>
       <c r="C39">
-        <v>464.7751480277891</v>
+        <v>458.9096938790062</v>
       </c>
       <c r="D39">
-        <v>620.7531480277891</v>
+        <v>621.7816938790062</v>
       </c>
       <c r="E39">
-        <v>145.478</v>
+        <v>152.372</v>
       </c>
       <c r="F39">
-        <v>255.078</v>
+        <v>261.972</v>
       </c>
       <c r="G39">
         <v>99.09999999999999</v>
@@ -4485,28 +4485,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M39">
-        <v>14.1058134</v>
+        <v>14.4870516</v>
       </c>
       <c r="N39">
-        <v>52.09418659999999</v>
+        <v>51.71294839999999</v>
       </c>
       <c r="O39">
-        <v>9.897895453999997</v>
+        <v>9.825460195999998</v>
       </c>
       <c r="P39">
-        <v>42.19629114599999</v>
+        <v>41.88748820399999</v>
       </c>
       <c r="Q39">
-        <v>79.29629114599999</v>
+        <v>78.98748820399999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1210201931210852</v>
+        <v>0.1220772173506854</v>
       </c>
       <c r="T39">
-        <v>1.268320518976359</v>
+        <v>1.286143466031269</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.693100505639752</v>
+        <v>4.569597860754495</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09270921475742497</v>
+        <v>0.09339204784856626</v>
       </c>
       <c r="C40">
-        <v>458.9096938790062</v>
+        <v>445.5048210783214</v>
       </c>
       <c r="D40">
-        <v>621.7816938790062</v>
+        <v>615.2708210783213</v>
       </c>
       <c r="E40">
-        <v>152.372</v>
+        <v>159.266</v>
       </c>
       <c r="F40">
-        <v>261.972</v>
+        <v>268.866</v>
       </c>
       <c r="G40">
         <v>99.09999999999999</v>
@@ -4567,45 +4567,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M40">
-        <v>14.4870516</v>
+        <v>15.5404548</v>
       </c>
       <c r="N40">
-        <v>51.71294839999999</v>
+        <v>50.65954519999999</v>
       </c>
       <c r="O40">
-        <v>9.825460195999998</v>
+        <v>9.625313587999997</v>
       </c>
       <c r="P40">
-        <v>41.88748820399999</v>
+        <v>41.03423161199999</v>
       </c>
       <c r="Q40">
-        <v>78.98748820399999</v>
+        <v>78.13423161199999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1220772173506854</v>
+        <v>0.1231688981124037</v>
       </c>
       <c r="T40">
-        <v>1.286143466031269</v>
+        <v>1.304550772006011</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.19</v>
       </c>
       <c r="W40">
-        <v>0.04479300000000001</v>
+        <v>0.04681800000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.569597860754495</v>
+        <v>4.25984958947276</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09339204784856626</v>
+        <v>0.09330538093970757</v>
       </c>
       <c r="C41">
-        <v>445.5048210783214</v>
+        <v>439.4296325662712</v>
       </c>
       <c r="D41">
-        <v>615.2708210783213</v>
+        <v>616.0896325662711</v>
       </c>
       <c r="E41">
-        <v>159.266</v>
+        <v>166.16</v>
       </c>
       <c r="F41">
-        <v>268.866</v>
+        <v>275.76</v>
       </c>
       <c r="G41">
         <v>99.09999999999999</v>
@@ -4649,28 +4649,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M41">
-        <v>15.5404548</v>
+        <v>15.938928</v>
       </c>
       <c r="N41">
-        <v>50.65954519999999</v>
+        <v>50.26107199999998</v>
       </c>
       <c r="O41">
-        <v>9.625313587999997</v>
+        <v>9.549603679999997</v>
       </c>
       <c r="P41">
-        <v>41.03423161199999</v>
+        <v>40.71146831999999</v>
       </c>
       <c r="Q41">
-        <v>78.13423161199999</v>
+        <v>77.81146831999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1231688981124037</v>
+        <v>0.1242969682328459</v>
       </c>
       <c r="T41">
-        <v>1.304550772006011</v>
+        <v>1.323571654846578</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.25984958947276</v>
+        <v>4.153353349735941</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09330538093970757</v>
+        <v>0.09321871403084886</v>
       </c>
       <c r="C42">
-        <v>439.4296325662712</v>
+        <v>433.3566263312497</v>
       </c>
       <c r="D42">
-        <v>616.0896325662711</v>
+        <v>616.9106263312497</v>
       </c>
       <c r="E42">
-        <v>166.16</v>
+        <v>173.054</v>
       </c>
       <c r="F42">
-        <v>275.76</v>
+        <v>282.654</v>
       </c>
       <c r="G42">
         <v>99.09999999999999</v>
@@ -4731,28 +4731,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M42">
-        <v>15.938928</v>
+        <v>16.3374012</v>
       </c>
       <c r="N42">
-        <v>50.26107199999998</v>
+        <v>49.86259879999999</v>
       </c>
       <c r="O42">
-        <v>9.549603679999997</v>
+        <v>9.473893771999997</v>
       </c>
       <c r="P42">
-        <v>40.71146831999999</v>
+        <v>40.38870502799999</v>
       </c>
       <c r="Q42">
-        <v>77.81146831999999</v>
+        <v>77.488705028</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1242969682328459</v>
+        <v>0.1254632780183879</v>
       </c>
       <c r="T42">
-        <v>1.323571654846578</v>
+        <v>1.343237313376656</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.153353349735941</v>
+        <v>4.052052048522869</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09321871403084886</v>
+        <v>0.09432274712199015</v>
       </c>
       <c r="C43">
-        <v>433.3566263312497</v>
+        <v>416.1650156990459</v>
       </c>
       <c r="D43">
-        <v>616.9106263312497</v>
+        <v>606.6130156990458</v>
       </c>
       <c r="E43">
-        <v>173.054</v>
+        <v>179.948</v>
       </c>
       <c r="F43">
-        <v>282.654</v>
+        <v>289.548</v>
       </c>
       <c r="G43">
         <v>99.09999999999999</v>
@@ -4813,45 +4813,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M43">
-        <v>16.3374012</v>
+        <v>17.7492924</v>
       </c>
       <c r="N43">
-        <v>49.86259879999999</v>
+        <v>48.45070759999999</v>
       </c>
       <c r="O43">
-        <v>9.473893771999997</v>
+        <v>9.205634443999998</v>
       </c>
       <c r="P43">
-        <v>40.38870502799999</v>
+        <v>39.24507315599999</v>
       </c>
       <c r="Q43">
-        <v>77.488705028</v>
+        <v>76.34507315599998</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1254632780183879</v>
+        <v>0.1266698053827416</v>
       </c>
       <c r="T43">
-        <v>1.343237313376656</v>
+        <v>1.363581098062944</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0.19</v>
       </c>
       <c r="W43">
-        <v>0.04681800000000001</v>
+        <v>0.049653</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.052052048522869</v>
+        <v>3.729726149533712</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09432274712199017</v>
+        <v>0.09426443021313144</v>
       </c>
       <c r="C44">
-        <v>416.1650156990457</v>
+        <v>409.8063455195415</v>
       </c>
       <c r="D44">
-        <v>606.6130156990457</v>
+        <v>607.1483455195415</v>
       </c>
       <c r="E44">
-        <v>179.948</v>
+        <v>186.842</v>
       </c>
       <c r="F44">
-        <v>289.548</v>
+        <v>296.442</v>
       </c>
       <c r="G44">
         <v>99.09999999999999</v>
@@ -4895,28 +4895,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M44">
-        <v>17.7492924</v>
+        <v>18.1718946</v>
       </c>
       <c r="N44">
-        <v>48.45070759999999</v>
+        <v>48.02810539999999</v>
       </c>
       <c r="O44">
-        <v>9.205634443999998</v>
+        <v>9.125340025999998</v>
       </c>
       <c r="P44">
-        <v>39.24507315599999</v>
+        <v>38.90276537399999</v>
       </c>
       <c r="Q44">
-        <v>76.34507315599998</v>
+        <v>76.00276537399999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1266698053827416</v>
+        <v>0.1279186670405815</v>
       </c>
       <c r="T44">
-        <v>1.363581098062943</v>
+        <v>1.384638699755767</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.729726149533712</v>
+        <v>3.642988332102696</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09426443021313144</v>
+        <v>0.09420611330427275</v>
       </c>
       <c r="C45">
-        <v>409.8063455195415</v>
+        <v>403.4486210208412</v>
       </c>
       <c r="D45">
-        <v>607.1483455195415</v>
+        <v>607.6846210208412</v>
       </c>
       <c r="E45">
-        <v>186.842</v>
+        <v>193.736</v>
       </c>
       <c r="F45">
-        <v>296.442</v>
+        <v>303.336</v>
       </c>
       <c r="G45">
         <v>99.09999999999999</v>
@@ -4977,28 +4977,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M45">
-        <v>18.1718946</v>
+        <v>18.5944968</v>
       </c>
       <c r="N45">
-        <v>48.02810539999999</v>
+        <v>47.60550319999999</v>
       </c>
       <c r="O45">
-        <v>9.125340025999998</v>
+        <v>9.045045607999997</v>
       </c>
       <c r="P45">
-        <v>38.90276537399999</v>
+        <v>38.56045759199999</v>
       </c>
       <c r="Q45">
-        <v>76.00276537399999</v>
+        <v>75.660457592</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1279186670405815</v>
+        <v>0.1292121309004871</v>
       </c>
       <c r="T45">
-        <v>1.384638699755767</v>
+        <v>1.406448358651907</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.642988332102696</v>
+        <v>3.560193142736725</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09420611330427275</v>
+        <v>0.09516839639541405</v>
       </c>
       <c r="C46">
-        <v>403.4486210208412</v>
+        <v>387.8249939552901</v>
       </c>
       <c r="D46">
-        <v>607.6846210208412</v>
+        <v>598.9549939552901</v>
       </c>
       <c r="E46">
-        <v>193.736</v>
+        <v>200.63</v>
       </c>
       <c r="F46">
-        <v>303.336</v>
+        <v>310.23</v>
       </c>
       <c r="G46">
         <v>99.09999999999999</v>
@@ -5059,45 +5059,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M46">
-        <v>18.5944968</v>
+        <v>19.885743</v>
       </c>
       <c r="N46">
-        <v>47.60550319999999</v>
+        <v>46.31425699999998</v>
       </c>
       <c r="O46">
-        <v>9.045045607999997</v>
+        <v>8.799708829999997</v>
       </c>
       <c r="P46">
-        <v>38.56045759199999</v>
+        <v>37.51454816999998</v>
       </c>
       <c r="Q46">
-        <v>75.660457592</v>
+        <v>74.61454816999998</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1292121309004871</v>
+        <v>0.1305526298098437</v>
       </c>
       <c r="T46">
-        <v>1.406448358651907</v>
+        <v>1.42905109605336</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.19</v>
       </c>
       <c r="W46">
-        <v>0.049653</v>
+        <v>0.05192100000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.560193142736725</v>
+        <v>3.329018181518286</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09516839639541405</v>
+        <v>0.09513275948655533</v>
       </c>
       <c r="C47">
-        <v>387.8249939552901</v>
+        <v>381.2498098131489</v>
       </c>
       <c r="D47">
-        <v>598.9549939552901</v>
+        <v>599.2738098131489</v>
       </c>
       <c r="E47">
-        <v>200.63</v>
+        <v>207.524</v>
       </c>
       <c r="F47">
-        <v>310.23</v>
+        <v>317.124</v>
       </c>
       <c r="G47">
         <v>99.09999999999999</v>
@@ -5141,28 +5141,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M47">
-        <v>19.885743</v>
+        <v>20.3276484</v>
       </c>
       <c r="N47">
-        <v>46.31425699999998</v>
+        <v>45.87235159999999</v>
       </c>
       <c r="O47">
-        <v>8.799708829999997</v>
+        <v>8.715746803999998</v>
       </c>
       <c r="P47">
-        <v>37.51454816999998</v>
+        <v>37.15660479599999</v>
       </c>
       <c r="Q47">
-        <v>74.61454816999998</v>
+        <v>74.25660479599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1305526298098437</v>
+        <v>0.1319427768269543</v>
       </c>
       <c r="T47">
-        <v>1.42905109605336</v>
+        <v>1.452490971877089</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.329018181518286</v>
+        <v>3.256648221050497</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09513275948655533</v>
+        <v>0.09509712257769663</v>
       </c>
       <c r="C48">
-        <v>381.2498098131489</v>
+        <v>374.674965254731</v>
       </c>
       <c r="D48">
-        <v>599.2738098131489</v>
+        <v>599.592965254731</v>
       </c>
       <c r="E48">
-        <v>207.524</v>
+        <v>214.418</v>
       </c>
       <c r="F48">
-        <v>317.124</v>
+        <v>324.018</v>
       </c>
       <c r="G48">
         <v>99.09999999999999</v>
@@ -5223,28 +5223,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M48">
-        <v>20.3276484</v>
+        <v>20.7695538</v>
       </c>
       <c r="N48">
-        <v>45.87235159999999</v>
+        <v>45.43044619999998</v>
       </c>
       <c r="O48">
-        <v>8.715746803999998</v>
+        <v>8.631784777999997</v>
       </c>
       <c r="P48">
-        <v>37.15660479599999</v>
+        <v>36.79866142199999</v>
       </c>
       <c r="Q48">
-        <v>74.25660479599999</v>
+        <v>73.89866142199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1319427768269543</v>
+        <v>0.1333853822220691</v>
       </c>
       <c r="T48">
-        <v>1.452490971877089</v>
+        <v>1.476815371316808</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.256648221050497</v>
+        <v>3.187357833368571</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09509712257769663</v>
+        <v>0.09506148566883793</v>
       </c>
       <c r="C49">
-        <v>374.674965254731</v>
+        <v>368.1004608228826</v>
       </c>
       <c r="D49">
-        <v>599.592965254731</v>
+        <v>599.9124608228826</v>
       </c>
       <c r="E49">
-        <v>214.418</v>
+        <v>221.312</v>
       </c>
       <c r="F49">
-        <v>324.018</v>
+        <v>330.912</v>
       </c>
       <c r="G49">
         <v>99.09999999999999</v>
@@ -5305,28 +5305,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M49">
-        <v>20.7695538</v>
+        <v>21.2114592</v>
       </c>
       <c r="N49">
-        <v>45.43044619999998</v>
+        <v>44.98854079999998</v>
       </c>
       <c r="O49">
-        <v>8.631784777999997</v>
+        <v>8.547822751999997</v>
       </c>
       <c r="P49">
-        <v>36.79866142199999</v>
+        <v>36.44071804799999</v>
       </c>
       <c r="Q49">
-        <v>73.89866142199999</v>
+        <v>73.54071804799999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1333853822220691</v>
+        <v>0.1348834724400729</v>
       </c>
       <c r="T49">
-        <v>1.476815371316808</v>
+        <v>1.502075324581132</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.187357833368571</v>
+        <v>3.120954545173392</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0950614856688379</v>
+        <v>0.09502584875997921</v>
       </c>
       <c r="C50">
-        <v>368.100460822883</v>
+        <v>361.5262970616071</v>
       </c>
       <c r="D50">
-        <v>599.912460822883</v>
+        <v>600.232297061607</v>
       </c>
       <c r="E50">
-        <v>221.312</v>
+        <v>228.206</v>
       </c>
       <c r="F50">
-        <v>330.912</v>
+        <v>337.806</v>
       </c>
       <c r="G50">
         <v>99.09999999999999</v>
@@ -5387,28 +5387,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M50">
-        <v>21.2114592</v>
+        <v>21.6533646</v>
       </c>
       <c r="N50">
-        <v>44.98854079999999</v>
+        <v>44.54663539999999</v>
       </c>
       <c r="O50">
-        <v>8.547822751999998</v>
+        <v>8.463860725999997</v>
       </c>
       <c r="P50">
-        <v>36.44071804799999</v>
+        <v>36.08277467399999</v>
       </c>
       <c r="Q50">
-        <v>73.540718048</v>
+        <v>73.182774674</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1348834724400729</v>
+        <v>0.1364403112940769</v>
       </c>
       <c r="T50">
-        <v>1.502075324581132</v>
+        <v>1.528325864247978</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.120954545173393</v>
+        <v>3.057261595271895</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09502584875997921</v>
+        <v>0.09814921185112051</v>
       </c>
       <c r="C51">
-        <v>361.5262970616071</v>
+        <v>327.8376265847118</v>
       </c>
       <c r="D51">
-        <v>600.232297061607</v>
+        <v>573.4376265847118</v>
       </c>
       <c r="E51">
-        <v>228.206</v>
+        <v>235.1</v>
       </c>
       <c r="F51">
-        <v>337.806</v>
+        <v>344.7</v>
       </c>
       <c r="G51">
         <v>99.09999999999999</v>
@@ -5469,45 +5469,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M51">
-        <v>21.6533646</v>
+        <v>24.78393</v>
       </c>
       <c r="N51">
-        <v>44.54663539999999</v>
+        <v>41.41606999999999</v>
       </c>
       <c r="O51">
-        <v>8.463860725999997</v>
+        <v>7.869053299999998</v>
       </c>
       <c r="P51">
-        <v>36.08277467399999</v>
+        <v>33.54701669999999</v>
       </c>
       <c r="Q51">
-        <v>73.182774674</v>
+        <v>70.64701669999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1364403112940769</v>
+        <v>0.138059423702241</v>
       </c>
       <c r="T51">
-        <v>1.528325864247978</v>
+        <v>1.555626425501498</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.19</v>
       </c>
       <c r="W51">
-        <v>0.05192100000000001</v>
+        <v>0.05823900000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.057261595271895</v>
+        <v>2.67108565913477</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09814921185112051</v>
+        <v>0.09817675494226182</v>
       </c>
       <c r="C52">
-        <v>327.8376265847118</v>
+        <v>320.7179770086859</v>
       </c>
       <c r="D52">
-        <v>573.4376265847118</v>
+        <v>573.2119770086858</v>
       </c>
       <c r="E52">
-        <v>235.1</v>
+        <v>241.994</v>
       </c>
       <c r="F52">
-        <v>344.7</v>
+        <v>351.594</v>
       </c>
       <c r="G52">
         <v>99.09999999999999</v>
@@ -5551,28 +5551,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M52">
-        <v>24.78393</v>
+        <v>25.2796086</v>
       </c>
       <c r="N52">
-        <v>41.41606999999999</v>
+        <v>40.92039139999999</v>
       </c>
       <c r="O52">
-        <v>7.869053299999998</v>
+        <v>7.774874365999997</v>
       </c>
       <c r="P52">
-        <v>33.54701669999999</v>
+        <v>33.14551703399999</v>
       </c>
       <c r="Q52">
-        <v>70.64701669999999</v>
+        <v>70.24551703399999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.138059423702241</v>
+        <v>0.1397446223311465</v>
       </c>
       <c r="T52">
-        <v>1.555626425501498</v>
+        <v>1.58404129537761</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.67108565913477</v>
+        <v>2.618711430524284</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09817675494226182</v>
+        <v>0.09820429803340311</v>
       </c>
       <c r="C53">
-        <v>320.7179770086859</v>
+        <v>313.5985049504943</v>
       </c>
       <c r="D53">
-        <v>573.2119770086858</v>
+        <v>572.9865049504942</v>
       </c>
       <c r="E53">
-        <v>241.994</v>
+        <v>248.888</v>
       </c>
       <c r="F53">
-        <v>351.594</v>
+        <v>358.488</v>
       </c>
       <c r="G53">
         <v>99.09999999999999</v>
@@ -5633,28 +5633,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M53">
-        <v>25.2796086</v>
+        <v>25.7752872</v>
       </c>
       <c r="N53">
-        <v>40.92039139999999</v>
+        <v>40.42471279999999</v>
       </c>
       <c r="O53">
-        <v>7.774874365999997</v>
+        <v>7.680695431999998</v>
       </c>
       <c r="P53">
-        <v>33.14551703399999</v>
+        <v>32.74401736799999</v>
       </c>
       <c r="Q53">
-        <v>70.24551703399999</v>
+        <v>69.84401736799998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1397446223311465</v>
+        <v>0.1415000375695898</v>
       </c>
       <c r="T53">
-        <v>1.58404129537761</v>
+        <v>1.613640118165228</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.618711430524284</v>
+        <v>2.568351595321894</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09820429803340311</v>
+        <v>0.09823184112454439</v>
       </c>
       <c r="C54">
-        <v>313.5985049504943</v>
+        <v>306.4792102007401</v>
       </c>
       <c r="D54">
-        <v>572.9865049504942</v>
+        <v>572.76121020074</v>
       </c>
       <c r="E54">
-        <v>248.888</v>
+        <v>255.782</v>
       </c>
       <c r="F54">
-        <v>358.488</v>
+        <v>365.382</v>
       </c>
       <c r="G54">
         <v>99.09999999999999</v>
@@ -5715,28 +5715,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M54">
-        <v>25.7752872</v>
+        <v>26.2709658</v>
       </c>
       <c r="N54">
-        <v>40.42471279999999</v>
+        <v>39.92903419999999</v>
       </c>
       <c r="O54">
-        <v>7.680695431999998</v>
+        <v>7.586516497999998</v>
       </c>
       <c r="P54">
-        <v>32.74401736799999</v>
+        <v>32.34251770199999</v>
       </c>
       <c r="Q54">
-        <v>69.84401736799998</v>
+        <v>69.442517702</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1415000375695898</v>
+        <v>0.1433301513288179</v>
       </c>
       <c r="T54">
-        <v>1.613640118165228</v>
+        <v>1.644498465326786</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.568351595321894</v>
+        <v>2.519892131259216</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09823184112454439</v>
+        <v>0.09996524421568569</v>
       </c>
       <c r="C55">
-        <v>306.4792102007401</v>
+        <v>285.7542857946033</v>
       </c>
       <c r="D55">
-        <v>572.76121020074</v>
+        <v>558.9302857946033</v>
       </c>
       <c r="E55">
-        <v>255.782</v>
+        <v>262.676</v>
       </c>
       <c r="F55">
-        <v>365.382</v>
+        <v>372.276</v>
       </c>
       <c r="G55">
         <v>99.09999999999999</v>
@@ -5797,45 +5797,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M55">
-        <v>26.2709658</v>
+        <v>28.2185208</v>
       </c>
       <c r="N55">
-        <v>39.92903419999999</v>
+        <v>37.98147919999998</v>
       </c>
       <c r="O55">
-        <v>7.586516497999998</v>
+        <v>7.216481047999997</v>
       </c>
       <c r="P55">
-        <v>32.34251770199999</v>
+        <v>30.76499815199998</v>
       </c>
       <c r="Q55">
-        <v>69.442517702</v>
+        <v>67.86499815199998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1433301513288179</v>
+        <v>0.1452398352514906</v>
       </c>
       <c r="T55">
-        <v>1.644498465326786</v>
+        <v>1.676698479756239</v>
       </c>
       <c r="U55">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.19</v>
       </c>
       <c r="W55">
-        <v>0.05823900000000001</v>
+        <v>0.06139800000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.519892131259216</v>
+        <v>2.34597697268384</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09996524421568569</v>
+        <v>0.100024377306827</v>
       </c>
       <c r="C56">
-        <v>285.7542857946033</v>
+        <v>278.4002319611084</v>
       </c>
       <c r="D56">
-        <v>558.9302857946033</v>
+        <v>558.4702319611084</v>
       </c>
       <c r="E56">
-        <v>262.676</v>
+        <v>269.5700000000001</v>
       </c>
       <c r="F56">
-        <v>372.276</v>
+        <v>379.17</v>
       </c>
       <c r="G56">
         <v>99.09999999999999</v>
@@ -5879,28 +5879,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M56">
-        <v>28.2185208</v>
+        <v>28.741086</v>
       </c>
       <c r="N56">
-        <v>37.98147919999998</v>
+        <v>37.45891399999999</v>
       </c>
       <c r="O56">
-        <v>7.216481047999997</v>
+        <v>7.117193659999997</v>
       </c>
       <c r="P56">
-        <v>30.76499815199998</v>
+        <v>30.34172033999999</v>
       </c>
       <c r="Q56">
-        <v>67.86499815199998</v>
+        <v>67.44172033999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1452398352514906</v>
+        <v>0.1472343940151711</v>
       </c>
       <c r="T56">
-        <v>1.676698479756239</v>
+        <v>1.710329605938111</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.34597697268384</v>
+        <v>2.303322845907771</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.100024377306827</v>
+        <v>0.1000835103979683</v>
       </c>
       <c r="C57">
-        <v>278.4002319611084</v>
+        <v>271.0469348426112</v>
       </c>
       <c r="D57">
-        <v>558.4702319611084</v>
+        <v>558.0109348426112</v>
       </c>
       <c r="E57">
-        <v>269.5700000000001</v>
+        <v>276.4640000000001</v>
       </c>
       <c r="F57">
-        <v>379.17</v>
+        <v>386.064</v>
       </c>
       <c r="G57">
         <v>99.09999999999999</v>
@@ -5961,28 +5961,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M57">
-        <v>28.741086</v>
+        <v>29.26365120000001</v>
       </c>
       <c r="N57">
-        <v>37.45891399999999</v>
+        <v>36.93634879999998</v>
       </c>
       <c r="O57">
-        <v>7.117193659999997</v>
+        <v>7.017906271999997</v>
       </c>
       <c r="P57">
-        <v>30.34172033999999</v>
+        <v>29.91844252799999</v>
       </c>
       <c r="Q57">
-        <v>67.44172033999999</v>
+        <v>67.01844252799998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1472343940151711</v>
+        <v>0.149319614540837</v>
       </c>
       <c r="T57">
-        <v>1.710329605938111</v>
+        <v>1.745489419673705</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.303322845907771</v>
+        <v>2.262192080802274</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1000835103979683</v>
+        <v>0.1001426434891096</v>
       </c>
       <c r="C58">
-        <v>271.0469348426112</v>
+        <v>263.6943925736327</v>
       </c>
       <c r="D58">
-        <v>558.0109348426112</v>
+        <v>557.5523925736327</v>
       </c>
       <c r="E58">
-        <v>276.4640000000001</v>
+        <v>283.3580000000001</v>
       </c>
       <c r="F58">
-        <v>386.064</v>
+        <v>392.958</v>
       </c>
       <c r="G58">
         <v>99.09999999999999</v>
@@ -6043,28 +6043,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M58">
-        <v>29.26365120000001</v>
+        <v>29.7862164</v>
       </c>
       <c r="N58">
-        <v>36.93634879999998</v>
+        <v>36.41378359999999</v>
       </c>
       <c r="O58">
-        <v>7.017906271999997</v>
+        <v>6.918618883999998</v>
       </c>
       <c r="P58">
-        <v>29.91844252799999</v>
+        <v>29.49516471599999</v>
       </c>
       <c r="Q58">
-        <v>67.01844252799998</v>
+        <v>66.595164716</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.149319614540837</v>
+        <v>0.1515018220676967</v>
       </c>
       <c r="T58">
-        <v>1.745489419673705</v>
+        <v>1.782284573583047</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.262192080802274</v>
+        <v>2.222504500437323</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1001426434891096</v>
+        <v>0.1002017765802509</v>
       </c>
       <c r="C59">
-        <v>263.6943925736327</v>
+        <v>256.3426032948211</v>
       </c>
       <c r="D59">
-        <v>557.5523925736327</v>
+        <v>557.0946032948211</v>
       </c>
       <c r="E59">
-        <v>283.3580000000001</v>
+        <v>290.2520000000001</v>
       </c>
       <c r="F59">
-        <v>392.958</v>
+        <v>399.852</v>
       </c>
       <c r="G59">
         <v>99.09999999999999</v>
@@ -6125,28 +6125,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M59">
-        <v>29.7862164</v>
+        <v>30.3087816</v>
       </c>
       <c r="N59">
-        <v>36.41378359999999</v>
+        <v>35.89121839999999</v>
       </c>
       <c r="O59">
-        <v>6.918618883999998</v>
+        <v>6.819331495999998</v>
       </c>
       <c r="P59">
-        <v>29.49516471599999</v>
+        <v>29.07188690399999</v>
       </c>
       <c r="Q59">
-        <v>66.595164716</v>
+        <v>66.17188690399999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1515018220676967</v>
+        <v>0.1537879442386925</v>
       </c>
       <c r="T59">
-        <v>1.782284573583047</v>
+        <v>1.820831877678549</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.222504500437323</v>
+        <v>2.184185457326334</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1002017765802509</v>
+        <v>0.1002609096713922</v>
       </c>
       <c r="C60">
-        <v>256.3426032948213</v>
+        <v>248.9915651529267</v>
       </c>
       <c r="D60">
-        <v>557.0946032948212</v>
+        <v>556.6375651529266</v>
       </c>
       <c r="E60">
-        <v>290.252</v>
+        <v>297.146</v>
       </c>
       <c r="F60">
-        <v>399.852</v>
+        <v>406.746</v>
       </c>
       <c r="G60">
         <v>99.09999999999999</v>
@@ -6207,28 +6207,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M60">
-        <v>30.3087816</v>
+        <v>30.8313468</v>
       </c>
       <c r="N60">
-        <v>35.89121839999999</v>
+        <v>35.36865319999998</v>
       </c>
       <c r="O60">
-        <v>6.819331495999998</v>
+        <v>6.720044107999997</v>
       </c>
       <c r="P60">
-        <v>29.07188690399999</v>
+        <v>28.64860909199999</v>
       </c>
       <c r="Q60">
-        <v>66.17188690399999</v>
+        <v>65.74860909199998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1537879442386925</v>
+        <v>0.1561855845643711</v>
       </c>
       <c r="T60">
-        <v>1.820831877678548</v>
+        <v>1.861259538071392</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.184185457326334</v>
+        <v>2.147165364829278</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1002609096713922</v>
+        <v>0.1003200427625335</v>
       </c>
       <c r="C61">
-        <v>248.9915651529267</v>
+        <v>241.6412763007754</v>
       </c>
       <c r="D61">
-        <v>556.6375651529266</v>
+        <v>556.1812763007754</v>
       </c>
       <c r="E61">
-        <v>297.146</v>
+        <v>304.04</v>
       </c>
       <c r="F61">
-        <v>406.746</v>
+        <v>413.64</v>
       </c>
       <c r="G61">
         <v>99.09999999999999</v>
@@ -6289,28 +6289,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M61">
-        <v>30.8313468</v>
+        <v>31.353912</v>
       </c>
       <c r="N61">
-        <v>35.36865319999998</v>
+        <v>34.84608799999999</v>
       </c>
       <c r="O61">
-        <v>6.720044107999997</v>
+        <v>6.620756719999997</v>
       </c>
       <c r="P61">
-        <v>28.64860909199999</v>
+        <v>28.22533127999999</v>
       </c>
       <c r="Q61">
-        <v>65.74860909199998</v>
+        <v>65.32533128</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1561855845643711</v>
+        <v>0.1587031069063336</v>
       </c>
       <c r="T61">
-        <v>1.861259538071392</v>
+        <v>1.903708581483877</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.147165364829278</v>
+        <v>2.111379275415457</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1003200427625335</v>
+        <v>0.1003791758536748</v>
       </c>
       <c r="C62">
-        <v>241.6412763007754</v>
+        <v>234.2917348972456</v>
       </c>
       <c r="D62">
-        <v>556.1812763007754</v>
+        <v>555.7257348972456</v>
       </c>
       <c r="E62">
-        <v>304.04</v>
+        <v>310.934</v>
       </c>
       <c r="F62">
-        <v>413.64</v>
+        <v>420.534</v>
       </c>
       <c r="G62">
         <v>99.09999999999999</v>
@@ -6371,28 +6371,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M62">
-        <v>31.353912</v>
+        <v>31.8764772</v>
       </c>
       <c r="N62">
-        <v>34.84608799999999</v>
+        <v>34.32352279999999</v>
       </c>
       <c r="O62">
-        <v>6.620756719999997</v>
+        <v>6.521469331999997</v>
       </c>
       <c r="P62">
-        <v>28.22533127999999</v>
+        <v>27.80205346799999</v>
       </c>
       <c r="Q62">
-        <v>65.32533128</v>
+        <v>64.90205346799999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1587031069063336</v>
+        <v>0.1613497329581404</v>
       </c>
       <c r="T62">
-        <v>1.903708581483877</v>
+        <v>1.948334498917516</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.111379275415457</v>
+        <v>2.076766500408645</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1003791758536748</v>
+        <v>0.100438308944816</v>
       </c>
       <c r="C63">
-        <v>234.2917348972456</v>
+        <v>226.9429391072426</v>
       </c>
       <c r="D63">
-        <v>555.7257348972456</v>
+        <v>555.2709391072426</v>
       </c>
       <c r="E63">
-        <v>310.934</v>
+        <v>317.828</v>
       </c>
       <c r="F63">
-        <v>420.534</v>
+        <v>427.428</v>
       </c>
       <c r="G63">
         <v>99.09999999999999</v>
@@ -6453,28 +6453,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M63">
-        <v>31.8764772</v>
+        <v>32.3990424</v>
       </c>
       <c r="N63">
-        <v>34.32352279999999</v>
+        <v>33.80095759999999</v>
       </c>
       <c r="O63">
-        <v>6.521469331999997</v>
+        <v>6.422181943999998</v>
       </c>
       <c r="P63">
-        <v>27.80205346799999</v>
+        <v>27.37877565599999</v>
       </c>
       <c r="Q63">
-        <v>64.90205346799999</v>
+        <v>64.478775656</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1613497329581404</v>
+        <v>0.1641356551179369</v>
       </c>
       <c r="T63">
-        <v>1.948334498917516</v>
+        <v>1.995309148847661</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.076766500408645</v>
+        <v>2.043270266531087</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.100438308944816</v>
+        <v>0.1004974420359573</v>
       </c>
       <c r="C64">
-        <v>226.9429391072426</v>
+        <v>219.5948871016735</v>
       </c>
       <c r="D64">
-        <v>555.2709391072426</v>
+        <v>554.8168871016735</v>
       </c>
       <c r="E64">
-        <v>317.828</v>
+        <v>324.722</v>
       </c>
       <c r="F64">
-        <v>427.428</v>
+        <v>434.322</v>
       </c>
       <c r="G64">
         <v>99.09999999999999</v>
@@ -6535,28 +6535,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M64">
-        <v>32.3990424</v>
+        <v>32.9216076</v>
       </c>
       <c r="N64">
-        <v>33.80095759999999</v>
+        <v>33.27839239999999</v>
       </c>
       <c r="O64">
-        <v>6.422181943999998</v>
+        <v>6.322894555999998</v>
       </c>
       <c r="P64">
-        <v>27.37877565599999</v>
+        <v>26.95549784399999</v>
       </c>
       <c r="Q64">
-        <v>64.478775656</v>
+        <v>64.05549784399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1641356551179369</v>
+        <v>0.1670721676647495</v>
       </c>
       <c r="T64">
-        <v>1.995309148847661</v>
+        <v>2.044822969044301</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.043270266531087</v>
+        <v>2.010837405157578</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1004974420359573</v>
+        <v>0.1079178551270986</v>
       </c>
       <c r="C65">
-        <v>219.5948871016735</v>
+        <v>161.068154402268</v>
       </c>
       <c r="D65">
-        <v>554.8168871016735</v>
+        <v>503.1841544022679</v>
       </c>
       <c r="E65">
-        <v>324.722</v>
+        <v>331.616</v>
       </c>
       <c r="F65">
-        <v>434.322</v>
+        <v>441.216</v>
       </c>
       <c r="G65">
         <v>99.09999999999999</v>
@@ -6617,45 +6617,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M65">
-        <v>32.9216076</v>
+        <v>39.70944</v>
       </c>
       <c r="N65">
-        <v>33.27839239999999</v>
+        <v>26.49055999999999</v>
       </c>
       <c r="O65">
-        <v>6.322894555999998</v>
+        <v>5.033206399999997</v>
       </c>
       <c r="P65">
-        <v>26.95549784399999</v>
+        <v>21.45735359999999</v>
       </c>
       <c r="Q65">
-        <v>64.05549784399999</v>
+        <v>58.55735359999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1670721676647495</v>
+        <v>0.1701718197974962</v>
       </c>
       <c r="T65">
-        <v>2.044822969044301</v>
+        <v>2.097087557029643</v>
       </c>
       <c r="U65">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V65">
         <v>0.19</v>
       </c>
       <c r="W65">
-        <v>0.06139800000000001</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>2.010837405157578</v>
+        <v>1.667109886213454</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1079178551270986</v>
+        <v>0.1080920082182399</v>
       </c>
       <c r="C66">
-        <v>161.068154402268</v>
+        <v>153.0775298142489</v>
       </c>
       <c r="D66">
-        <v>503.1841544022679</v>
+        <v>502.0875298142489</v>
       </c>
       <c r="E66">
-        <v>331.616</v>
+        <v>338.51</v>
       </c>
       <c r="F66">
-        <v>441.216</v>
+        <v>448.11</v>
       </c>
       <c r="G66">
         <v>99.09999999999999</v>
@@ -6699,28 +6699,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M66">
-        <v>39.70944</v>
+        <v>40.3299</v>
       </c>
       <c r="N66">
-        <v>26.49055999999999</v>
+        <v>25.87009999999999</v>
       </c>
       <c r="O66">
-        <v>5.033206399999997</v>
+        <v>4.915318999999998</v>
       </c>
       <c r="P66">
-        <v>21.45735359999999</v>
+        <v>20.95478099999999</v>
       </c>
       <c r="Q66">
-        <v>58.55735359999999</v>
+        <v>58.05478099999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1701718197974962</v>
+        <v>0.1734485949092569</v>
       </c>
       <c r="T66">
-        <v>2.097087557029643</v>
+        <v>2.152338692899862</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.667109886213454</v>
+        <v>1.64146204181017</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1080920082182399</v>
+        <v>0.1082661613093812</v>
       </c>
       <c r="C67">
-        <v>153.0775298142489</v>
+        <v>145.0916747337627</v>
       </c>
       <c r="D67">
-        <v>502.0875298142489</v>
+        <v>500.9956747337628</v>
       </c>
       <c r="E67">
-        <v>338.51</v>
+        <v>345.404</v>
       </c>
       <c r="F67">
-        <v>448.11</v>
+        <v>455.004</v>
       </c>
       <c r="G67">
         <v>99.09999999999999</v>
@@ -6781,28 +6781,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M67">
-        <v>40.3299</v>
+        <v>40.95036</v>
       </c>
       <c r="N67">
-        <v>25.87009999999999</v>
+        <v>25.24963999999999</v>
       </c>
       <c r="O67">
-        <v>4.915318999999998</v>
+        <v>4.797431599999998</v>
       </c>
       <c r="P67">
-        <v>20.95478099999999</v>
+        <v>20.45220839999999</v>
       </c>
       <c r="Q67">
-        <v>58.05478099999999</v>
+        <v>57.55220839999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1734485949092569</v>
+        <v>0.1769181214981801</v>
       </c>
       <c r="T67">
-        <v>2.152338692899862</v>
+        <v>2.210839895585977</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.64146204181017</v>
+        <v>1.616591404813046</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1082661613093812</v>
+        <v>0.1084403144005225</v>
       </c>
       <c r="C68">
-        <v>145.0916747337627</v>
+        <v>137.1105581125719</v>
       </c>
       <c r="D68">
-        <v>500.9956747337628</v>
+        <v>499.9085581125719</v>
       </c>
       <c r="E68">
-        <v>345.404</v>
+        <v>352.298</v>
       </c>
       <c r="F68">
-        <v>455.004</v>
+        <v>461.898</v>
       </c>
       <c r="G68">
         <v>99.09999999999999</v>
@@ -6863,28 +6863,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M68">
-        <v>40.95036</v>
+        <v>41.57082</v>
       </c>
       <c r="N68">
-        <v>25.24963999999999</v>
+        <v>24.62917999999999</v>
       </c>
       <c r="O68">
-        <v>4.797431599999998</v>
+        <v>4.679544199999999</v>
       </c>
       <c r="P68">
-        <v>20.45220839999999</v>
+        <v>19.94963579999999</v>
       </c>
       <c r="Q68">
-        <v>57.55220839999999</v>
+        <v>57.04963579999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1769181214981801</v>
+        <v>0.1805979224258258</v>
       </c>
       <c r="T68">
-        <v>2.210839895585977</v>
+        <v>2.272886625707613</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.616591404813046</v>
+        <v>1.592463174890464</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1084403144005225</v>
+        <v>0.1086144674916638</v>
       </c>
       <c r="C69">
-        <v>137.1105581125719</v>
+        <v>129.1341491713432</v>
       </c>
       <c r="D69">
-        <v>499.9085581125719</v>
+        <v>498.8261491713432</v>
       </c>
       <c r="E69">
-        <v>352.298</v>
+        <v>359.192</v>
       </c>
       <c r="F69">
-        <v>461.898</v>
+        <v>468.792</v>
       </c>
       <c r="G69">
         <v>99.09999999999999</v>
@@ -6945,28 +6945,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M69">
-        <v>41.57082</v>
+        <v>42.19128</v>
       </c>
       <c r="N69">
-        <v>24.62917999999999</v>
+        <v>24.00871999999999</v>
       </c>
       <c r="O69">
-        <v>4.679544199999999</v>
+        <v>4.561656799999998</v>
       </c>
       <c r="P69">
-        <v>19.94963579999999</v>
+        <v>19.44706319999999</v>
       </c>
       <c r="Q69">
-        <v>57.04963579999999</v>
+        <v>56.5470632</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1805979224258258</v>
+        <v>0.1845077109114494</v>
       </c>
       <c r="T69">
-        <v>2.272886625707613</v>
+        <v>2.338811276461851</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.592463174890464</v>
+        <v>1.569044598789133</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1086144674916638</v>
+        <v>0.1087886205828051</v>
       </c>
       <c r="C70">
-        <v>129.1341491713432</v>
+        <v>121.1624173967426</v>
       </c>
       <c r="D70">
-        <v>498.8261491713432</v>
+        <v>497.7484173967426</v>
       </c>
       <c r="E70">
-        <v>359.192</v>
+        <v>366.086</v>
       </c>
       <c r="F70">
-        <v>468.792</v>
+        <v>475.686</v>
       </c>
       <c r="G70">
         <v>99.09999999999999</v>
@@ -7027,28 +7027,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M70">
-        <v>42.19128</v>
+        <v>42.81174</v>
       </c>
       <c r="N70">
-        <v>24.00871999999999</v>
+        <v>23.38825999999999</v>
       </c>
       <c r="O70">
-        <v>4.561656799999998</v>
+        <v>4.443769399999998</v>
       </c>
       <c r="P70">
-        <v>19.44706319999999</v>
+        <v>18.94449059999999</v>
       </c>
       <c r="Q70">
-        <v>56.5470632</v>
+        <v>56.04449059999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1845077109114494</v>
+        <v>0.1886697438155003</v>
       </c>
       <c r="T70">
-        <v>2.338811276461851</v>
+        <v>2.408989130490558</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.569044598789133</v>
+        <v>1.546304821995088</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1087886205828051</v>
+        <v>0.1089627736739464</v>
       </c>
       <c r="C71">
-        <v>121.1624173967426</v>
+        <v>113.1953325385683</v>
       </c>
       <c r="D71">
-        <v>497.7484173967426</v>
+        <v>496.6753325385683</v>
       </c>
       <c r="E71">
-        <v>366.086</v>
+        <v>372.98</v>
       </c>
       <c r="F71">
-        <v>475.686</v>
+        <v>482.58</v>
       </c>
       <c r="G71">
         <v>99.09999999999999</v>
@@ -7109,28 +7109,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M71">
-        <v>42.81174</v>
+        <v>43.4322</v>
       </c>
       <c r="N71">
-        <v>23.38825999999999</v>
+        <v>22.76779999999999</v>
       </c>
       <c r="O71">
-        <v>4.443769399999998</v>
+        <v>4.325881999999997</v>
       </c>
       <c r="P71">
-        <v>18.94449059999999</v>
+        <v>18.44191799999999</v>
       </c>
       <c r="Q71">
-        <v>56.04449059999999</v>
+        <v>55.541918</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1886697438155003</v>
+        <v>0.1931092455798213</v>
       </c>
       <c r="T71">
-        <v>2.408989130490558</v>
+        <v>2.483845508121176</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.546304821995088</v>
+        <v>1.524214753109444</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1089627736739464</v>
+        <v>0.1091369267650877</v>
       </c>
       <c r="C72">
-        <v>113.1953325385683</v>
+        <v>105.2328646069203</v>
       </c>
       <c r="D72">
-        <v>496.6753325385683</v>
+        <v>495.6068646069204</v>
       </c>
       <c r="E72">
-        <v>372.98</v>
+        <v>379.874</v>
       </c>
       <c r="F72">
-        <v>482.58</v>
+        <v>489.474</v>
       </c>
       <c r="G72">
         <v>99.09999999999999</v>
@@ -7191,28 +7191,28 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M72">
-        <v>43.4322</v>
+        <v>44.05266</v>
       </c>
       <c r="N72">
-        <v>22.76779999999999</v>
+        <v>22.14733999999999</v>
       </c>
       <c r="O72">
-        <v>4.325881999999997</v>
+        <v>4.207994599999997</v>
       </c>
       <c r="P72">
-        <v>18.44191799999999</v>
+        <v>17.93934539999999</v>
       </c>
       <c r="Q72">
-        <v>55.541918</v>
+        <v>55.03934539999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1931092455798213</v>
+        <v>0.1978549198796128</v>
       </c>
       <c r="T72">
-        <v>2.483845508121176</v>
+        <v>2.563864394553908</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.524214753109444</v>
+        <v>1.502746939685367</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1091369267650877</v>
+        <v>0.1449122096296113</v>
       </c>
       <c r="C73">
-        <v>105.2328646069205</v>
+        <v>-53.55415498588525</v>
       </c>
       <c r="D73">
-        <v>495.6068646069205</v>
+        <v>343.7138450141147</v>
       </c>
       <c r="E73">
-        <v>379.8739999999999</v>
+        <v>386.7679999999999</v>
       </c>
       <c r="F73">
-        <v>489.4739999999999</v>
+        <v>496.3679999999999</v>
       </c>
       <c r="G73">
         <v>99.09999999999999</v>
@@ -7273,45 +7273,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M73">
-        <v>44.05265999999999</v>
+        <v>72.8668224</v>
       </c>
       <c r="N73">
-        <v>22.14734</v>
+        <v>-6.666822400000015</v>
       </c>
       <c r="O73">
-        <v>4.2079946</v>
+        <v>-1.266696256000003</v>
       </c>
       <c r="P73">
-        <v>17.9393454</v>
+        <v>-5.400126144000012</v>
       </c>
       <c r="Q73">
-        <v>55.0393454</v>
+        <v>31.69987385599999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1978549198796127</v>
+        <v>0.2052180722297546</v>
       </c>
       <c r="T73">
-        <v>2.563864394553907</v>
+        <v>2.688017721241075</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.19</v>
+        <v>0.172616282496216</v>
       </c>
       <c r="W73">
-        <v>0.07290000000000001</v>
+        <v>0.1214599297295555</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.502746939685367</v>
+        <v>0.9085067499800841</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1449122096296113</v>
+        <v>0.1459222096296113</v>
       </c>
       <c r="C74">
-        <v>-53.55415498588525</v>
+        <v>-63.39660847410312</v>
       </c>
       <c r="D74">
-        <v>343.7138450141147</v>
+        <v>340.7653915258968</v>
       </c>
       <c r="E74">
-        <v>386.7679999999999</v>
+        <v>393.6619999999999</v>
       </c>
       <c r="F74">
-        <v>496.3679999999999</v>
+        <v>503.2619999999999</v>
       </c>
       <c r="G74">
         <v>99.09999999999999</v>
@@ -7355,37 +7355,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M74">
-        <v>72.8668224</v>
+        <v>73.87886159999999</v>
       </c>
       <c r="N74">
-        <v>-6.666822400000015</v>
+        <v>-7.678861600000005</v>
       </c>
       <c r="O74">
-        <v>-1.266696256000003</v>
+        <v>-1.458983704000001</v>
       </c>
       <c r="P74">
-        <v>-5.400126144000012</v>
+        <v>-6.219877896000003</v>
       </c>
       <c r="Q74">
-        <v>31.69987385599999</v>
+        <v>30.880122104</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2052180722297546</v>
+        <v>0.2111224452753011</v>
       </c>
       <c r="T74">
-        <v>2.688017721241075</v>
+        <v>2.787573933138893</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.172616282496216</v>
+        <v>0.1702516758866788</v>
       </c>
       <c r="W74">
-        <v>0.1214599297295555</v>
+        <v>0.1218070539798356</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9085067499800841</v>
+        <v>0.8960614520351515</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1459222096296113</v>
+        <v>0.1469322096296113</v>
       </c>
       <c r="C75">
-        <v>-63.39660847410312</v>
+        <v>-73.18890722666197</v>
       </c>
       <c r="D75">
-        <v>340.7653915258968</v>
+        <v>337.867092773338</v>
       </c>
       <c r="E75">
-        <v>393.6619999999999</v>
+        <v>400.5559999999999</v>
       </c>
       <c r="F75">
-        <v>503.2619999999999</v>
+        <v>510.1559999999999</v>
       </c>
       <c r="G75">
         <v>99.09999999999999</v>
@@ -7437,37 +7437,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M75">
-        <v>73.87886159999999</v>
+        <v>74.8909008</v>
       </c>
       <c r="N75">
-        <v>-7.678861600000005</v>
+        <v>-8.690900800000009</v>
       </c>
       <c r="O75">
-        <v>-1.458983704000001</v>
+        <v>-1.651271152000002</v>
       </c>
       <c r="P75">
-        <v>-6.219877896000003</v>
+        <v>-7.039629648000007</v>
       </c>
       <c r="Q75">
-        <v>30.880122104</v>
+        <v>30.06037035199999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2111224452753011</v>
+        <v>0.2174810008628127</v>
       </c>
       <c r="T75">
-        <v>2.787573933138893</v>
+        <v>2.894788315182697</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1702516758866788</v>
+        <v>0.1679509775638858</v>
       </c>
       <c r="W75">
-        <v>0.1218070539798356</v>
+        <v>0.1221447964936216</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8960614520351515</v>
+        <v>0.8839525134941358</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1469322096296113</v>
+        <v>0.1479422096296112</v>
       </c>
       <c r="C76">
-        <v>-73.18890722666197</v>
+        <v>-82.93232018827621</v>
       </c>
       <c r="D76">
-        <v>337.867092773338</v>
+        <v>335.0176798117238</v>
       </c>
       <c r="E76">
-        <v>400.5559999999999</v>
+        <v>407.4499999999999</v>
       </c>
       <c r="F76">
-        <v>510.1559999999999</v>
+        <v>517.05</v>
       </c>
       <c r="G76">
         <v>99.09999999999999</v>
@@ -7519,37 +7519,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M76">
-        <v>74.8909008</v>
+        <v>75.90294</v>
       </c>
       <c r="N76">
-        <v>-8.690900800000009</v>
+        <v>-9.702940000000012</v>
       </c>
       <c r="O76">
-        <v>-1.651271152000002</v>
+        <v>-1.843558600000002</v>
       </c>
       <c r="P76">
-        <v>-7.039629648000007</v>
+        <v>-7.85938140000001</v>
       </c>
       <c r="Q76">
-        <v>30.06037035199999</v>
+        <v>29.24061859999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2174810008628127</v>
+        <v>0.2243482408973252</v>
       </c>
       <c r="T76">
-        <v>2.894788315182697</v>
+        <v>3.010579847790005</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1679509775638858</v>
+        <v>0.1657116311963673</v>
       </c>
       <c r="W76">
-        <v>0.1221447964936216</v>
+        <v>0.1224735325403733</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8839525134941358</v>
+        <v>0.8721664799808807</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1479422096296112</v>
+        <v>0.1489522096296113</v>
       </c>
       <c r="C77">
-        <v>-82.93232018827621</v>
+        <v>-92.62807385490976</v>
       </c>
       <c r="D77">
-        <v>335.0176798117238</v>
+        <v>332.2159261450902</v>
       </c>
       <c r="E77">
-        <v>407.4499999999999</v>
+        <v>414.3439999999999</v>
       </c>
       <c r="F77">
-        <v>517.05</v>
+        <v>523.944</v>
       </c>
       <c r="G77">
         <v>99.09999999999999</v>
@@ -7601,37 +7601,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M77">
-        <v>75.90294</v>
+        <v>76.9149792</v>
       </c>
       <c r="N77">
-        <v>-9.702940000000012</v>
+        <v>-10.71497920000002</v>
       </c>
       <c r="O77">
-        <v>-1.843558600000002</v>
+        <v>-2.035846048000003</v>
       </c>
       <c r="P77">
-        <v>-7.85938140000001</v>
+        <v>-8.679133152000013</v>
       </c>
       <c r="Q77">
-        <v>29.24061859999999</v>
+        <v>28.42086684799999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2243482408973252</v>
+        <v>0.2317877509347137</v>
       </c>
       <c r="T77">
-        <v>3.010579847790005</v>
+        <v>3.136020674781255</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1657116311963673</v>
+        <v>0.1635312149964151</v>
       </c>
       <c r="W77">
-        <v>0.1224735325403733</v>
+        <v>0.1227936176385263</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8721664799808807</v>
+        <v>0.8606906052442901</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1489522096296113</v>
+        <v>0.1499622096296113</v>
       </c>
       <c r="C78">
-        <v>-92.62807385490976</v>
+        <v>-102.2773540340493</v>
       </c>
       <c r="D78">
-        <v>332.2159261450902</v>
+        <v>329.4606459659507</v>
       </c>
       <c r="E78">
-        <v>414.3439999999999</v>
+        <v>421.2379999999999</v>
       </c>
       <c r="F78">
-        <v>523.944</v>
+        <v>530.838</v>
       </c>
       <c r="G78">
         <v>99.09999999999999</v>
@@ -7683,37 +7683,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M78">
-        <v>76.9149792</v>
+        <v>77.92701840000001</v>
       </c>
       <c r="N78">
-        <v>-10.71497920000002</v>
+        <v>-11.72701840000002</v>
       </c>
       <c r="O78">
-        <v>-2.035846048000003</v>
+        <v>-2.228133496000004</v>
       </c>
       <c r="P78">
-        <v>-8.679133152000013</v>
+        <v>-9.498884904000017</v>
       </c>
       <c r="Q78">
-        <v>28.42086684799999</v>
+        <v>27.60111509599999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2317877509347137</v>
+        <v>0.2398741748883969</v>
       </c>
       <c r="T78">
-        <v>3.136020674781255</v>
+        <v>3.272369399771744</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1635312149964151</v>
+        <v>0.1614074329834747</v>
       </c>
       <c r="W78">
-        <v>0.1227936176385263</v>
+        <v>0.1231053888380259</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8606906052442901</v>
+        <v>0.8495128051761824</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1499622096296113</v>
+        <v>0.1509722096296112</v>
       </c>
       <c r="C79">
-        <v>-102.2773540340493</v>
+        <v>-111.8813075181044</v>
       </c>
       <c r="D79">
-        <v>329.4606459659507</v>
+        <v>326.7506924818956</v>
       </c>
       <c r="E79">
-        <v>421.2379999999999</v>
+        <v>428.1319999999999</v>
       </c>
       <c r="F79">
-        <v>530.838</v>
+        <v>537.732</v>
       </c>
       <c r="G79">
         <v>99.09999999999999</v>
@@ -7765,37 +7765,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M79">
-        <v>77.92701840000001</v>
+        <v>78.9390576</v>
       </c>
       <c r="N79">
-        <v>-11.72701840000002</v>
+        <v>-12.73905760000001</v>
       </c>
       <c r="O79">
-        <v>-2.228133496000004</v>
+        <v>-2.420420944000002</v>
       </c>
       <c r="P79">
-        <v>-9.498884904000017</v>
+        <v>-10.31863665600001</v>
       </c>
       <c r="Q79">
-        <v>27.60111509599999</v>
+        <v>26.78136334399999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2398741748883969</v>
+        <v>0.248695728292415</v>
       </c>
       <c r="T79">
-        <v>3.272369399771744</v>
+        <v>3.421113463397733</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1614074329834747</v>
+        <v>0.159338106919584</v>
       </c>
       <c r="W79">
-        <v>0.1231053888380259</v>
+        <v>0.1234091659042051</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8495128051761824</v>
+        <v>0.8386216153662315</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1509722096296112</v>
+        <v>0.1519822096296113</v>
       </c>
       <c r="C80">
-        <v>-111.8813075181044</v>
+        <v>-121.4410436758948</v>
       </c>
       <c r="D80">
-        <v>326.7506924818956</v>
+        <v>324.0849563241052</v>
       </c>
       <c r="E80">
-        <v>428.1319999999999</v>
+        <v>435.026</v>
       </c>
       <c r="F80">
-        <v>537.732</v>
+        <v>544.626</v>
       </c>
       <c r="G80">
         <v>99.09999999999999</v>
@@ -7847,37 +7847,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M80">
-        <v>78.9390576</v>
+        <v>79.9510968</v>
       </c>
       <c r="N80">
-        <v>-12.73905760000001</v>
+        <v>-13.75109680000001</v>
       </c>
       <c r="O80">
-        <v>-2.420420944000002</v>
+        <v>-2.612708392000003</v>
       </c>
       <c r="P80">
-        <v>-10.31863665600001</v>
+        <v>-11.13838840800001</v>
       </c>
       <c r="Q80">
-        <v>26.78136334399999</v>
+        <v>25.96161159199999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.248695728292415</v>
+        <v>0.2583574296396729</v>
       </c>
       <c r="T80">
-        <v>3.421113463397733</v>
+        <v>3.584023628321436</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.159338106919584</v>
+        <v>0.1573211688573108</v>
       </c>
       <c r="W80">
-        <v>0.1234091659042051</v>
+        <v>0.1237052524117468</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8386216153662315</v>
+        <v>0.8280061518805829</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1519822096296113</v>
+        <v>0.1529922096296112</v>
       </c>
       <c r="C81">
-        <v>-121.4410436758948</v>
+        <v>-130.9576359668638</v>
       </c>
       <c r="D81">
-        <v>324.0849563241052</v>
+        <v>321.4623640331362</v>
       </c>
       <c r="E81">
-        <v>435.026</v>
+        <v>441.92</v>
       </c>
       <c r="F81">
-        <v>544.626</v>
+        <v>551.52</v>
       </c>
       <c r="G81">
         <v>99.09999999999999</v>
@@ -7929,37 +7929,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M81">
-        <v>79.9510968</v>
+        <v>80.96313600000001</v>
       </c>
       <c r="N81">
-        <v>-13.75109680000001</v>
+        <v>-14.76313600000002</v>
       </c>
       <c r="O81">
-        <v>-2.612708392000003</v>
+        <v>-2.804995840000003</v>
       </c>
       <c r="P81">
-        <v>-11.13838840800001</v>
+        <v>-11.95814016000001</v>
       </c>
       <c r="Q81">
-        <v>25.96161159199999</v>
+        <v>25.14185983999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2583574296396729</v>
+        <v>0.2689853011216565</v>
       </c>
       <c r="T81">
-        <v>3.584023628321436</v>
+        <v>3.763224809737507</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1573211688573108</v>
+        <v>0.1553546542465944</v>
       </c>
       <c r="W81">
-        <v>0.1237052524117468</v>
+        <v>0.1239939367566</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8280061518805829</v>
+        <v>0.8176560749820756</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1529922096296112</v>
+        <v>0.1540022096296113</v>
       </c>
       <c r="C82">
-        <v>-130.9576359668638</v>
+        <v>-140.4321233823637</v>
       </c>
       <c r="D82">
-        <v>321.4623640331362</v>
+        <v>318.8818766176363</v>
       </c>
       <c r="E82">
-        <v>441.92</v>
+        <v>448.814</v>
       </c>
       <c r="F82">
-        <v>551.52</v>
+        <v>558.414</v>
       </c>
       <c r="G82">
         <v>99.09999999999999</v>
@@ -8011,37 +8011,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M82">
-        <v>80.96313600000001</v>
+        <v>81.97517520000001</v>
       </c>
       <c r="N82">
-        <v>-14.76313600000002</v>
+        <v>-15.77517520000002</v>
       </c>
       <c r="O82">
-        <v>-2.804995840000003</v>
+        <v>-2.997283288000004</v>
       </c>
       <c r="P82">
-        <v>-11.95814016000001</v>
+        <v>-12.77789191200002</v>
       </c>
       <c r="Q82">
-        <v>25.14185983999999</v>
+        <v>24.32210808799999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2689853011216565</v>
+        <v>0.2807318959175332</v>
       </c>
       <c r="T82">
-        <v>3.763224809737507</v>
+        <v>3.961289273407902</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1553546542465944</v>
+        <v>0.1534366955521919</v>
       </c>
       <c r="W82">
-        <v>0.1239939367566</v>
+        <v>0.1242754930929382</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8176560749820756</v>
+        <v>0.8075615555378524</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1540022096296113</v>
+        <v>0.2009958442997563</v>
       </c>
       <c r="C83">
-        <v>-140.4321233823637</v>
+        <v>-234.0404407428565</v>
       </c>
       <c r="D83">
-        <v>318.8818766176363</v>
+        <v>232.1675592571435</v>
       </c>
       <c r="E83">
-        <v>448.814</v>
+        <v>455.708</v>
       </c>
       <c r="F83">
-        <v>558.414</v>
+        <v>565.308</v>
       </c>
       <c r="G83">
         <v>99.09999999999999</v>
@@ -8093,45 +8093,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M83">
-        <v>81.97517520000001</v>
+        <v>113.5138464</v>
       </c>
       <c r="N83">
-        <v>-15.77517520000002</v>
+        <v>-47.31384640000002</v>
       </c>
       <c r="O83">
-        <v>-2.997283288000004</v>
+        <v>-8.989630816000004</v>
       </c>
       <c r="P83">
-        <v>-12.77789191200002</v>
+        <v>-38.32421558400002</v>
       </c>
       <c r="Q83">
-        <v>24.32210808799999</v>
+        <v>-1.224215584000014</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2807318959175332</v>
+        <v>0.303248304969313</v>
       </c>
       <c r="T83">
-        <v>3.961289273407902</v>
+        <v>4.340948277580709</v>
       </c>
       <c r="U83">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1534366955521919</v>
+        <v>0.1108058655300751</v>
       </c>
       <c r="W83">
-        <v>0.1242754930929382</v>
+        <v>0.1785501822015609</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8075615555378524</v>
+        <v>0.5831887659477636</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2009958442997563</v>
+        <v>0.2025458442997563</v>
       </c>
       <c r="C84">
-        <v>-234.0404407428565</v>
+        <v>-242.9982866170149</v>
       </c>
       <c r="D84">
-        <v>232.1675592571435</v>
+        <v>230.1037133829852</v>
       </c>
       <c r="E84">
-        <v>455.708</v>
+        <v>462.602</v>
       </c>
       <c r="F84">
-        <v>565.308</v>
+        <v>572.202</v>
       </c>
       <c r="G84">
         <v>99.09999999999999</v>
@@ -8175,37 +8175,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M84">
-        <v>113.5138464</v>
+        <v>114.8981616</v>
       </c>
       <c r="N84">
-        <v>-47.31384640000002</v>
+        <v>-48.69816160000002</v>
       </c>
       <c r="O84">
-        <v>-8.989630816000004</v>
+        <v>-9.252650704000004</v>
       </c>
       <c r="P84">
-        <v>-38.32421558400002</v>
+        <v>-39.44551089600002</v>
       </c>
       <c r="Q84">
-        <v>-1.224215584000014</v>
+        <v>-2.345510896000015</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.303248304969313</v>
+        <v>0.3183923229086844</v>
       </c>
       <c r="T84">
-        <v>4.340948277580709</v>
+        <v>4.596298176261927</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1108058655300751</v>
+        <v>0.1094708551020019</v>
       </c>
       <c r="W84">
-        <v>0.1785501822015609</v>
+        <v>0.178818252295518</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5831887659477636</v>
+        <v>0.5761623952736941</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2025458442997563</v>
+        <v>0.2040958442997563</v>
       </c>
       <c r="C85">
-        <v>-242.9982866170149</v>
+        <v>-251.919762818286</v>
       </c>
       <c r="D85">
-        <v>230.1037133829852</v>
+        <v>228.076237181714</v>
       </c>
       <c r="E85">
-        <v>462.602</v>
+        <v>469.496</v>
       </c>
       <c r="F85">
-        <v>572.202</v>
+        <v>579.096</v>
       </c>
       <c r="G85">
         <v>99.09999999999999</v>
@@ -8257,37 +8257,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M85">
-        <v>114.8981616</v>
+        <v>116.2824768</v>
       </c>
       <c r="N85">
-        <v>-48.69816160000002</v>
+        <v>-50.08247680000001</v>
       </c>
       <c r="O85">
-        <v>-9.252650704000004</v>
+        <v>-9.515670592000001</v>
       </c>
       <c r="P85">
-        <v>-39.44551089600002</v>
+        <v>-40.56680620800001</v>
       </c>
       <c r="Q85">
-        <v>-2.345510896000015</v>
+        <v>-3.466806208000008</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3183923229086844</v>
+        <v>0.3354293430904773</v>
       </c>
       <c r="T85">
-        <v>4.596298176261927</v>
+        <v>4.883566812278299</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1094708551020019</v>
+        <v>0.1081676306365019</v>
       </c>
       <c r="W85">
-        <v>0.178818252295518</v>
+        <v>0.1790799397681904</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5761623952736941</v>
+        <v>0.5693033191394835</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2040958442997563</v>
+        <v>0.2056458442997563</v>
       </c>
       <c r="C86">
-        <v>-251.9197628182859</v>
+        <v>-260.8058223247639</v>
       </c>
       <c r="D86">
-        <v>228.0762371817141</v>
+        <v>226.0841776752361</v>
       </c>
       <c r="E86">
-        <v>469.496</v>
+        <v>476.39</v>
       </c>
       <c r="F86">
-        <v>579.096</v>
+        <v>585.99</v>
       </c>
       <c r="G86">
         <v>99.09999999999999</v>
@@ -8339,37 +8339,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M86">
-        <v>116.2824768</v>
+        <v>117.666792</v>
       </c>
       <c r="N86">
-        <v>-50.08247680000001</v>
+        <v>-51.46679200000001</v>
       </c>
       <c r="O86">
-        <v>-9.515670592000001</v>
+        <v>-9.778690480000002</v>
       </c>
       <c r="P86">
-        <v>-40.56680620800001</v>
+        <v>-41.68810152000001</v>
       </c>
       <c r="Q86">
-        <v>-3.466806208000008</v>
+        <v>-4.588101520000009</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3354293430904771</v>
+        <v>0.3547379659631755</v>
       </c>
       <c r="T86">
-        <v>4.883566812278295</v>
+        <v>5.209137933096848</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1081676306365019</v>
+        <v>0.1068950702760724</v>
       </c>
       <c r="W86">
-        <v>0.1790799397681904</v>
+        <v>0.1793354698885647</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5693033191394835</v>
+        <v>0.5626056330319602</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2056458442997563</v>
+        <v>0.2071958442997563</v>
       </c>
       <c r="C87">
-        <v>-260.8058223247639</v>
+        <v>-269.657385108882</v>
       </c>
       <c r="D87">
-        <v>226.0841776752361</v>
+        <v>224.1266148911181</v>
       </c>
       <c r="E87">
-        <v>476.39</v>
+        <v>483.284</v>
       </c>
       <c r="F87">
-        <v>585.99</v>
+        <v>592.884</v>
       </c>
       <c r="G87">
         <v>99.09999999999999</v>
@@ -8421,37 +8421,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M87">
-        <v>117.666792</v>
+        <v>119.0511072</v>
       </c>
       <c r="N87">
-        <v>-51.46679200000001</v>
+        <v>-52.85110720000002</v>
       </c>
       <c r="O87">
-        <v>-9.778690480000002</v>
+        <v>-10.041710368</v>
       </c>
       <c r="P87">
-        <v>-41.68810152000001</v>
+        <v>-42.80939683200001</v>
       </c>
       <c r="Q87">
-        <v>-4.588101520000009</v>
+        <v>-5.70939683200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3547379659631755</v>
+        <v>0.3768049635319738</v>
       </c>
       <c r="T87">
-        <v>5.209137933096848</v>
+        <v>5.581219214032338</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1068950702760724</v>
+        <v>0.1056521043426297</v>
       </c>
       <c r="W87">
-        <v>0.1793354698885647</v>
+        <v>0.179585057448</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5626056330319602</v>
+        <v>0.5560637070664722</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2071958442997563</v>
+        <v>0.2087458442997563</v>
       </c>
       <c r="C88">
-        <v>-269.657385108882</v>
+        <v>-278.4753395540524</v>
       </c>
       <c r="D88">
-        <v>224.1266148911181</v>
+        <v>222.2026604459476</v>
       </c>
       <c r="E88">
-        <v>483.284</v>
+        <v>490.178</v>
       </c>
       <c r="F88">
-        <v>592.884</v>
+        <v>599.778</v>
       </c>
       <c r="G88">
         <v>99.09999999999999</v>
@@ -8503,37 +8503,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M88">
-        <v>119.0511072</v>
+        <v>120.4354224</v>
       </c>
       <c r="N88">
-        <v>-52.85110720000002</v>
+        <v>-54.23542240000002</v>
       </c>
       <c r="O88">
-        <v>-10.041710368</v>
+        <v>-10.304730256</v>
       </c>
       <c r="P88">
-        <v>-42.80939683200001</v>
+        <v>-43.93069214400001</v>
       </c>
       <c r="Q88">
-        <v>-5.70939683200001</v>
+        <v>-6.830692144000011</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3768049635319738</v>
+        <v>0.402266883803664</v>
       </c>
       <c r="T88">
-        <v>5.581219214032338</v>
+        <v>6.010543768957902</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1056521043426297</v>
+        <v>0.1044377123386915</v>
       </c>
       <c r="W88">
-        <v>0.179585057448</v>
+        <v>0.1798289073623908</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5560637070664722</v>
+        <v>0.5496721702036392</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2087458442997563</v>
+        <v>0.2102958442997563</v>
       </c>
       <c r="C89">
-        <v>-278.4753395540524</v>
+        <v>-287.260543798965</v>
       </c>
       <c r="D89">
-        <v>222.2026604459476</v>
+        <v>220.311456201035</v>
       </c>
       <c r="E89">
-        <v>490.178</v>
+        <v>497.072</v>
       </c>
       <c r="F89">
-        <v>599.778</v>
+        <v>606.672</v>
       </c>
       <c r="G89">
         <v>99.09999999999999</v>
@@ -8585,37 +8585,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M89">
-        <v>120.4354224</v>
+        <v>121.8197376</v>
       </c>
       <c r="N89">
-        <v>-54.23542240000002</v>
+        <v>-55.61973760000002</v>
       </c>
       <c r="O89">
-        <v>-10.304730256</v>
+        <v>-10.56775014400001</v>
       </c>
       <c r="P89">
-        <v>-43.93069214400001</v>
+        <v>-45.05198745600002</v>
       </c>
       <c r="Q89">
-        <v>-6.830692144000011</v>
+        <v>-7.951987456000019</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.402266883803664</v>
+        <v>0.4319724574539694</v>
       </c>
       <c r="T89">
-        <v>6.010543768957902</v>
+        <v>6.511422416371062</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1044377123386915</v>
+        <v>0.1032509201530245</v>
       </c>
       <c r="W89">
-        <v>0.1798289073623908</v>
+        <v>0.1800672152332727</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5496721702036392</v>
+        <v>0.5434258955422342</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2102958442997563</v>
+        <v>0.2118458442997563</v>
       </c>
       <c r="C90">
-        <v>-287.260543798965</v>
+        <v>-296.0138270138137</v>
       </c>
       <c r="D90">
-        <v>220.311456201035</v>
+        <v>218.4521729861864</v>
       </c>
       <c r="E90">
-        <v>497.072</v>
+        <v>503.966</v>
       </c>
       <c r="F90">
-        <v>606.672</v>
+        <v>613.566</v>
       </c>
       <c r="G90">
         <v>99.09999999999999</v>
@@ -8667,37 +8667,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M90">
-        <v>121.8197376</v>
+        <v>123.2040528</v>
       </c>
       <c r="N90">
-        <v>-55.61973760000002</v>
+        <v>-57.00405280000003</v>
       </c>
       <c r="O90">
-        <v>-10.56775014400001</v>
+        <v>-10.83077003200001</v>
       </c>
       <c r="P90">
-        <v>-45.05198745600002</v>
+        <v>-46.17328276800002</v>
       </c>
       <c r="Q90">
-        <v>-7.951987456000019</v>
+        <v>-9.07328276800002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4319724574539694</v>
+        <v>0.4670790444952394</v>
       </c>
       <c r="T90">
-        <v>6.511422416371062</v>
+        <v>7.103369908768431</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1032509201530245</v>
+        <v>0.1020907974546759</v>
       </c>
       <c r="W90">
-        <v>0.1800672152332727</v>
+        <v>0.1803001678711011</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5434258955422342</v>
+        <v>0.5373199866035574</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2118458442997563</v>
+        <v>0.2133958442997563</v>
       </c>
       <c r="C91">
-        <v>-296.0138270138137</v>
+        <v>-304.7359906124418</v>
       </c>
       <c r="D91">
-        <v>218.4521729861864</v>
+        <v>216.6240093875582</v>
       </c>
       <c r="E91">
-        <v>503.966</v>
+        <v>510.86</v>
       </c>
       <c r="F91">
-        <v>613.566</v>
+        <v>620.46</v>
       </c>
       <c r="G91">
         <v>99.09999999999999</v>
@@ -8749,37 +8749,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M91">
-        <v>123.2040528</v>
+        <v>124.588368</v>
       </c>
       <c r="N91">
-        <v>-57.00405280000003</v>
+        <v>-58.38836800000003</v>
       </c>
       <c r="O91">
-        <v>-10.83077003200001</v>
+        <v>-11.09378992000001</v>
       </c>
       <c r="P91">
-        <v>-46.17328276800002</v>
+        <v>-47.29457808000002</v>
       </c>
       <c r="Q91">
-        <v>-9.07328276800002</v>
+        <v>-10.19457808000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4670790444952394</v>
+        <v>0.5092069489447634</v>
       </c>
       <c r="T91">
-        <v>7.103369908768431</v>
+        <v>7.813706899645275</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1020907974546759</v>
+        <v>0.1009564552607351</v>
       </c>
       <c r="W91">
-        <v>0.1803001678711011</v>
+        <v>0.1805279437836444</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5373199866035574</v>
+        <v>0.5313497645301846</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2133958442997563</v>
+        <v>0.2149458442997563</v>
       </c>
       <c r="C92">
-        <v>-304.7359906124418</v>
+        <v>-313.4278094041284</v>
       </c>
       <c r="D92">
-        <v>216.6240093875582</v>
+        <v>214.8261905958717</v>
       </c>
       <c r="E92">
-        <v>510.86</v>
+        <v>517.754</v>
       </c>
       <c r="F92">
-        <v>620.46</v>
+        <v>627.354</v>
       </c>
       <c r="G92">
         <v>99.09999999999999</v>
@@ -8831,37 +8831,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M92">
-        <v>124.588368</v>
+        <v>125.9726832</v>
       </c>
       <c r="N92">
-        <v>-58.38836800000003</v>
+        <v>-59.77268320000002</v>
       </c>
       <c r="O92">
-        <v>-11.09378992000001</v>
+        <v>-11.356809808</v>
       </c>
       <c r="P92">
-        <v>-47.29457808000002</v>
+        <v>-48.41587339200002</v>
       </c>
       <c r="Q92">
-        <v>-10.19457808000002</v>
+        <v>-11.31587339200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5092069489447634</v>
+        <v>0.560696609938626</v>
       </c>
       <c r="T92">
-        <v>7.813706899645275</v>
+        <v>8.681896555161417</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1009564552607351</v>
+        <v>0.09984704366446326</v>
       </c>
       <c r="W92">
-        <v>0.1805279437836444</v>
+        <v>0.1807507136321758</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5313497645301846</v>
+        <v>0.525510756128754</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2149458442997563</v>
+        <v>0.2164958442997563</v>
       </c>
       <c r="C93">
-        <v>-313.4278094041284</v>
+        <v>-322.0900326884915</v>
       </c>
       <c r="D93">
-        <v>214.8261905958717</v>
+        <v>213.0579673115086</v>
       </c>
       <c r="E93">
-        <v>517.754</v>
+        <v>524.648</v>
       </c>
       <c r="F93">
-        <v>627.354</v>
+        <v>634.248</v>
       </c>
       <c r="G93">
         <v>99.09999999999999</v>
@@ -8913,37 +8913,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M93">
-        <v>125.9726832</v>
+        <v>127.3569984</v>
       </c>
       <c r="N93">
-        <v>-59.77268320000002</v>
+        <v>-61.15699840000002</v>
       </c>
       <c r="O93">
-        <v>-11.356809808</v>
+        <v>-11.619829696</v>
       </c>
       <c r="P93">
-        <v>-48.41587339200002</v>
+        <v>-49.53716870400002</v>
       </c>
       <c r="Q93">
-        <v>-11.31587339200001</v>
+        <v>-12.43716870400002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.560696609938626</v>
+        <v>0.6250586861809544</v>
       </c>
       <c r="T93">
-        <v>8.681896555161417</v>
+        <v>9.767133624556596</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.09984704366446326</v>
+        <v>0.09876174971158866</v>
       </c>
       <c r="W93">
-        <v>0.1807507136321758</v>
+        <v>0.180968640657913</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.525510756128754</v>
+        <v>0.5197986826925719</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2164958442997563</v>
+        <v>0.2180458442997563</v>
       </c>
       <c r="C94">
-        <v>-322.0900326884915</v>
+        <v>-330.7233852967614</v>
       </c>
       <c r="D94">
-        <v>213.0579673115086</v>
+        <v>211.3186147032387</v>
       </c>
       <c r="E94">
-        <v>524.648</v>
+        <v>531.542</v>
       </c>
       <c r="F94">
-        <v>634.248</v>
+        <v>641.1420000000001</v>
       </c>
       <c r="G94">
         <v>99.09999999999999</v>
@@ -8995,37 +8995,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M94">
-        <v>127.3569984</v>
+        <v>128.7413136</v>
       </c>
       <c r="N94">
-        <v>-61.15699840000002</v>
+        <v>-62.54131360000002</v>
       </c>
       <c r="O94">
-        <v>-11.619829696</v>
+        <v>-11.882849584</v>
       </c>
       <c r="P94">
-        <v>-49.53716870400002</v>
+        <v>-50.65846401600002</v>
       </c>
       <c r="Q94">
-        <v>-12.43716870400002</v>
+        <v>-13.55846401600002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6250586861809544</v>
+        <v>0.7078099270639479</v>
       </c>
       <c r="T94">
-        <v>9.767133624556596</v>
+        <v>11.16243842806468</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.09876174971158866</v>
+        <v>0.09769979541361458</v>
       </c>
       <c r="W94">
-        <v>0.180968640657913</v>
+        <v>0.1811818810809462</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5197986826925719</v>
+        <v>0.51420944954534</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2180458442997563</v>
+        <v>0.2195958442997563</v>
       </c>
       <c r="C95">
-        <v>-330.7233852967614</v>
+        <v>-339.3285685824623</v>
       </c>
       <c r="D95">
-        <v>211.3186147032387</v>
+        <v>209.6074314175378</v>
       </c>
       <c r="E95">
-        <v>531.542</v>
+        <v>538.436</v>
       </c>
       <c r="F95">
-        <v>641.1420000000001</v>
+        <v>648.0360000000001</v>
       </c>
       <c r="G95">
         <v>99.09999999999999</v>
@@ -9077,37 +9077,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M95">
-        <v>128.7413136</v>
+        <v>130.1256288</v>
       </c>
       <c r="N95">
-        <v>-62.54131360000002</v>
+        <v>-63.92562880000003</v>
       </c>
       <c r="O95">
-        <v>-11.882849584</v>
+        <v>-12.145869472</v>
       </c>
       <c r="P95">
-        <v>-50.65846401600002</v>
+        <v>-51.77975932800003</v>
       </c>
       <c r="Q95">
-        <v>-13.55846401600002</v>
+        <v>-14.67975932800002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7078099270639479</v>
+        <v>0.8181449149079395</v>
       </c>
       <c r="T95">
-        <v>11.16243842806468</v>
+        <v>13.02284483274213</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.09769979541361458</v>
+        <v>0.09666043588793784</v>
       </c>
       <c r="W95">
-        <v>0.1811818810809462</v>
+        <v>0.1813905844737021</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.51420944954534</v>
+        <v>0.5087391362523044</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2195958442997563</v>
+        <v>0.2211458442997563</v>
       </c>
       <c r="C96">
-        <v>-339.3285685824623</v>
+        <v>-347.9062613643472</v>
       </c>
       <c r="D96">
-        <v>209.6074314175378</v>
+        <v>207.9237386356529</v>
       </c>
       <c r="E96">
-        <v>538.436</v>
+        <v>545.33</v>
       </c>
       <c r="F96">
-        <v>648.0360000000001</v>
+        <v>654.9300000000001</v>
       </c>
       <c r="G96">
         <v>99.09999999999999</v>
@@ -9159,37 +9159,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M96">
-        <v>130.1256288</v>
+        <v>131.509944</v>
       </c>
       <c r="N96">
-        <v>-63.92562880000003</v>
+        <v>-65.30994400000003</v>
       </c>
       <c r="O96">
-        <v>-12.145869472</v>
+        <v>-12.40888936000001</v>
       </c>
       <c r="P96">
-        <v>-51.77975932800003</v>
+        <v>-52.90105464000003</v>
       </c>
       <c r="Q96">
-        <v>-14.67975932800002</v>
+        <v>-15.80105464000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8181449149079395</v>
+        <v>0.9726138978895279</v>
       </c>
       <c r="T96">
-        <v>13.02284483274213</v>
+        <v>15.62741379929057</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.09666043588793784</v>
+        <v>0.09564295761543322</v>
       </c>
       <c r="W96">
-        <v>0.1813905844737021</v>
+        <v>0.181594894110821</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5087391362523044</v>
+        <v>0.5033839874496485</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2211458442997563</v>
+        <v>0.2569832814667846</v>
       </c>
       <c r="C97">
-        <v>-347.9062613643472</v>
+        <v>-387.3676487830367</v>
       </c>
       <c r="D97">
-        <v>207.9237386356529</v>
+        <v>175.3563512169634</v>
       </c>
       <c r="E97">
-        <v>545.33</v>
+        <v>552.224</v>
       </c>
       <c r="F97">
-        <v>654.9300000000001</v>
+        <v>661.8240000000001</v>
       </c>
       <c r="G97">
         <v>99.09999999999999</v>
@@ -9241,45 +9241,45 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M97">
-        <v>131.509944</v>
+        <v>156.0580992</v>
       </c>
       <c r="N97">
-        <v>-65.30994400000003</v>
+        <v>-89.85809920000003</v>
       </c>
       <c r="O97">
-        <v>-12.40888936000001</v>
+        <v>-17.07303884800001</v>
       </c>
       <c r="P97">
-        <v>-52.90105464000003</v>
+        <v>-72.78506035200002</v>
       </c>
       <c r="Q97">
-        <v>-15.80105464000003</v>
+        <v>-35.68506035200001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9726138978895279</v>
+        <v>1.221503301537619</v>
       </c>
       <c r="T97">
-        <v>15.62741379929057</v>
+        <v>19.82404670469289</v>
       </c>
       <c r="U97">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09564295761543322</v>
+        <v>0.0805981878830932</v>
       </c>
       <c r="W97">
-        <v>0.181594894110821</v>
+        <v>0.2167949472971666</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5033839874496485</v>
+        <v>0.4242009888583853</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2569832814667846</v>
+        <v>0.2588832814667846</v>
       </c>
       <c r="C98">
-        <v>-387.3676487830365</v>
+        <v>-395.7058424770184</v>
       </c>
       <c r="D98">
-        <v>175.3563512169634</v>
+        <v>173.9121575229816</v>
       </c>
       <c r="E98">
-        <v>552.2239999999999</v>
+        <v>559.1179999999999</v>
       </c>
       <c r="F98">
-        <v>661.824</v>
+        <v>668.718</v>
       </c>
       <c r="G98">
         <v>99.09999999999999</v>
@@ -9323,37 +9323,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M98">
-        <v>156.0580992</v>
+        <v>157.6837044</v>
       </c>
       <c r="N98">
-        <v>-89.8580992</v>
+        <v>-91.48370440000002</v>
       </c>
       <c r="O98">
-        <v>-17.073038848</v>
+        <v>-17.381903836</v>
       </c>
       <c r="P98">
-        <v>-72.785060352</v>
+        <v>-74.10180056400002</v>
       </c>
       <c r="Q98">
-        <v>-35.685060352</v>
+        <v>-37.00180056400001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.221503301537616</v>
+        <v>1.613404402050155</v>
       </c>
       <c r="T98">
-        <v>19.82404670469283</v>
+        <v>26.43206227292378</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08059818788309323</v>
+        <v>0.07976727872965926</v>
       </c>
       <c r="W98">
-        <v>0.2167949472971666</v>
+        <v>0.2169908756755463</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4242009888583853</v>
+        <v>0.4198277827876803</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2588832814667846</v>
+        <v>0.2607832814667846</v>
       </c>
       <c r="C99">
-        <v>-395.7058424770184</v>
+        <v>-404.0204424040603</v>
       </c>
       <c r="D99">
-        <v>173.9121575229816</v>
+        <v>172.4915575959397</v>
       </c>
       <c r="E99">
-        <v>559.1179999999999</v>
+        <v>566.0119999999999</v>
       </c>
       <c r="F99">
-        <v>668.718</v>
+        <v>675.612</v>
       </c>
       <c r="G99">
         <v>99.09999999999999</v>
@@ -9405,37 +9405,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M99">
-        <v>157.6837044</v>
+        <v>159.3093096</v>
       </c>
       <c r="N99">
-        <v>-91.48370440000002</v>
+        <v>-93.10930960000002</v>
       </c>
       <c r="O99">
-        <v>-17.381903836</v>
+        <v>-17.690768824</v>
       </c>
       <c r="P99">
-        <v>-74.10180056400002</v>
+        <v>-75.41854077600001</v>
       </c>
       <c r="Q99">
-        <v>-37.00180056400001</v>
+        <v>-38.31854077600001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.613404402050155</v>
+        <v>2.397206603075231</v>
       </c>
       <c r="T99">
-        <v>26.43206227292378</v>
+        <v>39.64809340938567</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07976727872965926</v>
+        <v>0.07895332690588723</v>
       </c>
       <c r="W99">
-        <v>0.2169908756755463</v>
+        <v>0.2171828055155918</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4198277827876803</v>
+        <v>0.415543825820459</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2607832814667846</v>
+        <v>0.2626832814667847</v>
       </c>
       <c r="C100">
-        <v>-404.0204424040603</v>
+        <v>-412.3120220560314</v>
       </c>
       <c r="D100">
-        <v>172.4915575959397</v>
+        <v>171.0939779439686</v>
       </c>
       <c r="E100">
-        <v>566.0119999999999</v>
+        <v>572.9059999999999</v>
       </c>
       <c r="F100">
-        <v>675.612</v>
+        <v>682.506</v>
       </c>
       <c r="G100">
         <v>99.09999999999999</v>
@@ -9487,37 +9487,37 @@
         <v>66.19999999999999</v>
       </c>
       <c r="M100">
-        <v>159.3093096</v>
+        <v>160.9349148</v>
       </c>
       <c r="N100">
-        <v>-93.10930960000002</v>
+        <v>-94.73491480000001</v>
       </c>
       <c r="O100">
-        <v>-17.690768824</v>
+        <v>-17.999633812</v>
       </c>
       <c r="P100">
-        <v>-75.41854077600001</v>
+        <v>-76.73528098800001</v>
       </c>
       <c r="Q100">
-        <v>-38.31854077600001</v>
+        <v>-39.63528098800001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.397206603075231</v>
+        <v>4.748613206150463</v>
       </c>
       <c r="T100">
-        <v>39.64809340938567</v>
+        <v>79.29618681877133</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07895332690588723</v>
+        <v>0.0781558185533025</v>
       </c>
       <c r="W100">
-        <v>0.2171828055155918</v>
+        <v>0.2173708579851313</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.415543825820459</v>
+        <v>0.4113464134384343</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2626832814667847</v>
-      </c>
-      <c r="C101">
-        <v>-412.3120220560314</v>
-      </c>
-      <c r="D101">
-        <v>171.0939779439686</v>
-      </c>
-      <c r="E101">
-        <v>572.9059999999999</v>
-      </c>
-      <c r="F101">
-        <v>682.506</v>
-      </c>
-      <c r="G101">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="H101">
-        <v>579.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>103.3</v>
-      </c>
-      <c r="K101">
-        <v>37.1</v>
-      </c>
-      <c r="L101">
-        <v>66.19999999999999</v>
-      </c>
-      <c r="M101">
-        <v>160.9349148</v>
-      </c>
-      <c r="N101">
-        <v>-94.73491480000001</v>
-      </c>
-      <c r="O101">
-        <v>-17.999633812</v>
-      </c>
-      <c r="P101">
-        <v>-76.73528098800001</v>
-      </c>
-      <c r="Q101">
-        <v>-39.63528098800001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.748613206150463</v>
-      </c>
-      <c r="T101">
-        <v>79.29618681877133</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0781558185533025</v>
-      </c>
-      <c r="W101">
-        <v>0.2173708579851313</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4113464134384343</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
